--- a/Inseason 25 Nordbord and CMJ.xlsx
+++ b/Inseason 25 Nordbord and CMJ.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjbourqu/Library/CloudStorage/Box-Box/2025 Football/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sachinvenkat/git/ProTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098F9611-2575-2C4C-931A-FECEC2782A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BD5354-44AC-A546-ADE7-F00736BF56DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="920" windowWidth="28220" windowHeight="16280" xr2:uid="{68F18A4E-16B6-C849-8DAE-51593F9DA775}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16720" xr2:uid="{68F18A4E-16B6-C849-8DAE-51593F9DA775}"/>
   </bookViews>
   <sheets>
     <sheet name="CMJ Inseason" sheetId="2" r:id="rId1"/>
     <sheet name="Nordbord Inseason" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CMJ Inseason'!$A$1:$CB$46</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="81">
   <si>
     <t xml:space="preserve">L AVG </t>
   </si>
@@ -96,9 +99,6 @@
     <t>Derrell Porter</t>
   </si>
   <si>
-    <t>Elijah Simonson</t>
-  </si>
-  <si>
     <t>Ernesto Nava</t>
   </si>
   <si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Matteo Perez</t>
-  </si>
-  <si>
-    <t>Mitch Dixon</t>
   </si>
   <si>
     <t>Nate Rutchena</t>
@@ -264,19 +261,25 @@
     <t>9.361702127659576</t>
   </si>
   <si>
-    <t>PJ Pickett</t>
-  </si>
-  <si>
-    <t>William Fowler</t>
-  </si>
-  <si>
-    <t>Dave Main</t>
-  </si>
-  <si>
     <t>Scott Nixon</t>
   </si>
   <si>
     <t>Will Fowler</t>
+  </si>
+  <si>
+    <t>David Main</t>
+  </si>
+  <si>
+    <t>Eli Simonson</t>
+  </si>
+  <si>
+    <t>Mitchell Dixon</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Laviel Pickett</t>
   </si>
 </sst>
 </file>
@@ -1716,12 +1719,6 @@
     <xf numFmtId="0" fontId="23" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1732,6 +1729,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2495,40 +2498,40 @@
         <v>8</v>
       </c>
       <c r="DC1" s="97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="DD1" s="98" t="s">
-        <v>48</v>
-      </c>
-      <c r="DE1" s="159" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="DE1" s="157" t="s">
+        <v>47</v>
       </c>
       <c r="DF1" s="87" t="s">
+        <v>56</v>
+      </c>
+      <c r="DG1" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="DH1" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="DG1" s="88" t="s">
+      <c r="DI1" s="88" t="s">
+        <v>62</v>
+      </c>
+      <c r="DJ1" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="DK1" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="DL1" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="DH1" s="89" t="s">
+      <c r="DM1" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="DI1" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="DJ1" s="88" t="s">
-        <v>65</v>
-      </c>
-      <c r="DK1" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="DL1" s="87" t="s">
+      <c r="DN1" s="89" t="s">
         <v>61</v>
-      </c>
-      <c r="DM1" s="88" t="s">
-        <v>62</v>
-      </c>
-      <c r="DN1" s="89" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.2">
@@ -3882,7 +3885,7 @@
     </row>
     <row r="7" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B7" s="28">
         <v>45861</v>
@@ -3917,7 +3920,7 @@
       <c r="X7" s="27"/>
       <c r="Y7" s="49"/>
       <c r="Z7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA7" s="28">
         <v>45904</v>
@@ -3932,7 +3935,7 @@
         <v>-1.36</v>
       </c>
       <c r="AE7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF7" s="28">
         <v>45918</v>
@@ -3947,7 +3950,7 @@
         <v>-1.4</v>
       </c>
       <c r="AJ7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AK7" s="28">
         <v>45925</v>
@@ -3962,7 +3965,7 @@
         <v>-1.34</v>
       </c>
       <c r="AO7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AP7" s="28">
         <v>45932</v>
@@ -3977,7 +3980,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AT7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AU7" s="28">
         <v>45939</v>
@@ -3992,7 +3995,7 @@
         <v>-1.32</v>
       </c>
       <c r="AY7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ7" s="28">
         <v>45946</v>
@@ -4007,7 +4010,7 @@
         <v>-1.39</v>
       </c>
       <c r="BD7" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BE7" s="28">
         <v>45953</v>
@@ -4022,7 +4025,7 @@
         <v>-1.38</v>
       </c>
       <c r="BI7" s="121" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BJ7" s="117">
         <v>45960</v>
@@ -4037,7 +4040,7 @@
         <v>-1.33</v>
       </c>
       <c r="BN7" s="141" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BO7" s="135">
         <v>45967</v>
@@ -4052,7 +4055,7 @@
         <v>-1.39</v>
       </c>
       <c r="BS7" s="141" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BT7" s="135">
         <v>45974</v>
@@ -4087,7 +4090,7 @@
       <c r="CZ7" s="19"/>
       <c r="DA7" s="8"/>
       <c r="DB7" s="79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="DC7" s="64">
         <f t="shared" si="4"/>
@@ -4727,7 +4730,7 @@
     </row>
     <row r="10" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="B10" s="28">
         <v>45861</v>
@@ -4742,7 +4745,7 @@
         <v>-1.45</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G10" s="28">
         <v>45870</v>
@@ -4757,7 +4760,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="L10" s="28">
         <v>45883</v>
@@ -4772,7 +4775,7 @@
         <v>-1.27</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="28">
         <v>45889</v>
@@ -4787,7 +4790,7 @@
         <v>-1.36</v>
       </c>
       <c r="U10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V10" s="28">
         <v>45897</v>
@@ -4802,7 +4805,7 @@
         <v>-1.39</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA10" s="28">
         <v>45904</v>
@@ -4817,7 +4820,7 @@
         <v>-1.36</v>
       </c>
       <c r="AE10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF10" s="28">
         <v>45918</v>
@@ -4832,7 +4835,7 @@
         <v>-1.32</v>
       </c>
       <c r="AJ10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AK10" s="28">
         <v>45925</v>
@@ -4847,7 +4850,7 @@
         <v>-1.31</v>
       </c>
       <c r="AO10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AP10" s="28">
         <v>45932</v>
@@ -4862,7 +4865,7 @@
         <v>-1.36</v>
       </c>
       <c r="AT10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AU10" s="28">
         <v>45939</v>
@@ -4877,7 +4880,7 @@
         <v>-1.26</v>
       </c>
       <c r="AY10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AZ10" s="28">
         <v>45946</v>
@@ -4892,7 +4895,7 @@
         <v>-1.33</v>
       </c>
       <c r="BD10" s="30" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="BE10" s="28">
         <v>45953</v>
@@ -4907,7 +4910,7 @@
         <v>-1.38</v>
       </c>
       <c r="BI10" s="121" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="BJ10" s="117">
         <v>45960</v>
@@ -4922,7 +4925,7 @@
         <v>-1.24</v>
       </c>
       <c r="BN10" s="141" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="BO10" s="135">
         <v>45967</v>
@@ -4937,7 +4940,7 @@
         <v>-1.23</v>
       </c>
       <c r="BS10" s="141" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="BT10" s="135">
         <v>45974</v>
@@ -4972,7 +4975,7 @@
       <c r="CZ10" s="19"/>
       <c r="DA10" s="8"/>
       <c r="DB10" s="79" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="DC10" s="64">
         <f t="shared" si="4"/>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="11" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="28">
         <v>45861</v>
@@ -5013,7 +5016,7 @@
         <v>-1.41</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="28">
         <v>45870</v>
@@ -5028,7 +5031,7 @@
         <v>-1.33</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L11" s="28">
         <v>45883</v>
@@ -5043,7 +5046,7 @@
         <v>-0.99</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q11" s="28">
         <v>45889</v>
@@ -5058,7 +5061,7 @@
         <v>-1.51</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V11" s="28">
         <v>45897</v>
@@ -5073,7 +5076,7 @@
         <v>-1</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA11" s="28">
         <v>45904</v>
@@ -5088,7 +5091,7 @@
         <v>-1.23</v>
       </c>
       <c r="AE11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF11" s="28">
         <v>45918</v>
@@ -5103,7 +5106,7 @@
         <v>-1</v>
       </c>
       <c r="AJ11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK11" s="28">
         <v>45925</v>
@@ -5118,7 +5121,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AO11" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP11" s="28">
         <v>45932</v>
@@ -5148,7 +5151,7 @@
       <c r="BG11" s="27"/>
       <c r="BH11" s="49"/>
       <c r="BI11" s="121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BJ11" s="117">
         <v>45960</v>
@@ -5163,7 +5166,7 @@
         <v>-1.35</v>
       </c>
       <c r="BN11" s="141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BO11" s="135">
         <v>45967</v>
@@ -5183,7 +5186,7 @@
       <c r="BV11" s="27"/>
       <c r="BW11" s="49"/>
       <c r="BX11" s="141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY11" s="135">
         <v>45981</v>
@@ -5212,7 +5215,7 @@
       <c r="CZ11" s="19"/>
       <c r="DA11" s="8"/>
       <c r="DB11" s="79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DC11" s="64">
         <f t="shared" si="4"/>
@@ -5265,7 +5268,7 @@
     </row>
     <row r="12" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="93">
         <v>45883</v>
@@ -5285,7 +5288,7 @@
       <c r="I12" s="27"/>
       <c r="J12" s="49"/>
       <c r="K12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L12" s="28">
         <v>45883</v>
@@ -5300,7 +5303,7 @@
         <v>-1.34</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="28">
         <v>45889</v>
@@ -5315,7 +5318,7 @@
         <v>-1.3</v>
       </c>
       <c r="U12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V12" s="28">
         <v>45897</v>
@@ -5330,7 +5333,7 @@
         <v>-1.26</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AA12" s="28">
         <v>45904</v>
@@ -5345,7 +5348,7 @@
         <v>-1.41</v>
       </c>
       <c r="AE12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF12" s="28">
         <v>45918</v>
@@ -5360,7 +5363,7 @@
         <v>-1.41</v>
       </c>
       <c r="AJ12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK12" s="28">
         <v>45925</v>
@@ -5375,7 +5378,7 @@
         <v>-1.53</v>
       </c>
       <c r="AO12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AP12" s="28">
         <v>45932</v>
@@ -5390,7 +5393,7 @@
         <v>-1.48</v>
       </c>
       <c r="AT12" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AU12" s="28">
         <v>45939</v>
@@ -5449,7 +5452,7 @@
       <c r="CZ12" s="19"/>
       <c r="DA12" s="8"/>
       <c r="DB12" s="79" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="DC12" s="64">
         <f t="shared" si="4"/>
@@ -5475,7 +5478,7 @@
     </row>
     <row r="13" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="28">
         <v>45861</v>
@@ -5490,7 +5493,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="28">
         <v>45870</v>
@@ -5505,7 +5508,7 @@
         <v>-1.24</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" s="28">
         <v>45883</v>
@@ -5520,7 +5523,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="28">
         <v>45889</v>
@@ -5535,7 +5538,7 @@
         <v>-1.24</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V13" s="28">
         <v>45897</v>
@@ -5550,7 +5553,7 @@
         <v>-1.42</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA13" s="28">
         <v>45904</v>
@@ -5565,7 +5568,7 @@
         <v>-1.19</v>
       </c>
       <c r="AE13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF13" s="28">
         <v>45918</v>
@@ -5580,7 +5583,7 @@
         <v>-1.35</v>
       </c>
       <c r="AJ13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK13" s="28">
         <v>45925</v>
@@ -5595,7 +5598,7 @@
         <v>-1.37</v>
       </c>
       <c r="AO13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP13" s="28">
         <v>45932</v>
@@ -5610,7 +5613,7 @@
         <v>-1.39</v>
       </c>
       <c r="AT13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU13" s="28">
         <v>45939</v>
@@ -5625,7 +5628,7 @@
         <v>-1.31</v>
       </c>
       <c r="AY13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" s="28">
         <v>45946</v>
@@ -5640,7 +5643,7 @@
         <v>-1.37</v>
       </c>
       <c r="BD13" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE13" s="28">
         <v>45953</v>
@@ -5655,7 +5658,7 @@
         <v>-1.26</v>
       </c>
       <c r="BI13" s="121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BJ13" s="117">
         <v>45960</v>
@@ -5670,7 +5673,7 @@
         <v>-1.19</v>
       </c>
       <c r="BN13" s="141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BO13" s="135">
         <v>45967</v>
@@ -5685,7 +5688,7 @@
         <v>-1.25</v>
       </c>
       <c r="BS13" s="141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT13" s="135">
         <v>45974</v>
@@ -5700,7 +5703,7 @@
         <v>-1.19</v>
       </c>
       <c r="BX13" s="141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY13" s="135">
         <v>45981</v>
@@ -5729,7 +5732,7 @@
       <c r="CZ13" s="19"/>
       <c r="DA13" s="8"/>
       <c r="DB13" s="79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DC13" s="64">
         <f t="shared" si="4"/>
@@ -5782,7 +5785,7 @@
     </row>
     <row r="14" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="28">
         <v>45861</v>
@@ -5797,7 +5800,7 @@
         <v>-1.41</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" s="28">
         <v>45870</v>
@@ -5812,7 +5815,7 @@
         <v>-1.39</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" s="28">
         <v>45883</v>
@@ -5827,7 +5830,7 @@
         <v>-1.32</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="28">
         <v>45889</v>
@@ -5842,7 +5845,7 @@
         <v>-1.52</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V14" s="28">
         <v>45897</v>
@@ -5857,7 +5860,7 @@
         <v>-1.48</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA14" s="28">
         <v>45904</v>
@@ -5872,7 +5875,7 @@
         <v>-1.47</v>
       </c>
       <c r="AE14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF14" s="28">
         <v>45918</v>
@@ -5887,7 +5890,7 @@
         <v>-1.31</v>
       </c>
       <c r="AJ14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" s="28">
         <v>45925</v>
@@ -5902,7 +5905,7 @@
         <v>-1.68</v>
       </c>
       <c r="AO14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP14" s="28">
         <v>45932</v>
@@ -5917,7 +5920,7 @@
         <v>-1.41</v>
       </c>
       <c r="AT14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU14" s="28">
         <v>45939</v>
@@ -5932,7 +5935,7 @@
         <v>-1.25</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ14" s="28">
         <v>45946</v>
@@ -5947,7 +5950,7 @@
         <v>-1.19</v>
       </c>
       <c r="BD14" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE14" s="28">
         <v>45953</v>
@@ -5962,7 +5965,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BI14" s="121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BJ14" s="117">
         <v>45960</v>
@@ -5977,7 +5980,7 @@
         <v>-1.41</v>
       </c>
       <c r="BN14" s="141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BO14" s="135">
         <v>45967</v>
@@ -5992,7 +5995,7 @@
         <v>-1.33</v>
       </c>
       <c r="BS14" s="141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT14" s="135">
         <v>45974</v>
@@ -6007,7 +6010,7 @@
         <v>-1.3</v>
       </c>
       <c r="BX14" s="141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY14" s="135">
         <v>45981</v>
@@ -6036,7 +6039,7 @@
       <c r="CZ14" s="19"/>
       <c r="DA14" s="8"/>
       <c r="DB14" s="79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DC14" s="64">
         <f t="shared" si="4"/>
@@ -6089,7 +6092,7 @@
     </row>
     <row r="15" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="28">
         <v>45861</v>
@@ -6104,7 +6107,7 @@
         <v>-1.22</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="28">
         <v>45870</v>
@@ -6119,7 +6122,7 @@
         <v>-1.3</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="28">
         <v>45883</v>
@@ -6134,7 +6137,7 @@
         <v>-1.22</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q15" s="28">
         <v>45889</v>
@@ -6149,7 +6152,7 @@
         <v>-1.07</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V15" s="28">
         <v>45897</v>
@@ -6174,7 +6177,7 @@
       <c r="AH15" s="26"/>
       <c r="AI15" s="40"/>
       <c r="AJ15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK15" s="28">
         <v>45925</v>
@@ -6194,7 +6197,7 @@
       <c r="AR15" s="27"/>
       <c r="AS15" s="49"/>
       <c r="AT15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU15" s="28">
         <v>45939</v>
@@ -6214,7 +6217,7 @@
       <c r="BB15" s="27"/>
       <c r="BC15" s="49"/>
       <c r="BD15" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE15" s="28">
         <v>45953</v>
@@ -6229,7 +6232,7 @@
         <v>-1.19</v>
       </c>
       <c r="BI15" s="121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BJ15" s="117">
         <v>45960</v>
@@ -6274,7 +6277,7 @@
       <c r="CZ15" s="19"/>
       <c r="DA15" s="8"/>
       <c r="DB15" s="79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="DC15" s="64">
         <f t="shared" si="4"/>
@@ -6300,7 +6303,7 @@
     </row>
     <row r="16" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="28">
         <v>45861</v>
@@ -6315,7 +6318,7 @@
         <v>-1.47</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" s="28">
         <v>45870</v>
@@ -6330,7 +6333,7 @@
         <v>-1.45</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L16" s="28">
         <v>45883</v>
@@ -6345,7 +6348,7 @@
         <v>-1.56</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="28">
         <v>45889</v>
@@ -6360,7 +6363,7 @@
         <v>-1.51</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V16" s="28">
         <v>45897</v>
@@ -6385,7 +6388,7 @@
       <c r="AH16" s="26"/>
       <c r="AI16" s="40"/>
       <c r="AJ16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" s="28">
         <v>45925</v>
@@ -6400,7 +6403,7 @@
         <v>-1.29</v>
       </c>
       <c r="AO16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP16" s="28">
         <v>45932</v>
@@ -6415,7 +6418,7 @@
         <v>-1.23</v>
       </c>
       <c r="AT16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU16" s="28">
         <v>45939</v>
@@ -6430,7 +6433,7 @@
         <v>-1.38</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ16" s="28">
         <v>45946</v>
@@ -6445,7 +6448,7 @@
         <v>-1.29</v>
       </c>
       <c r="BD16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE16" s="28">
         <v>45953</v>
@@ -6460,7 +6463,7 @@
         <v>-1.18</v>
       </c>
       <c r="BI16" s="121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BJ16" s="117">
         <v>45960</v>
@@ -6475,7 +6478,7 @@
         <v>-1.19</v>
       </c>
       <c r="BN16" s="141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BO16" s="135">
         <v>45967</v>
@@ -6490,7 +6493,7 @@
         <v>-1.22</v>
       </c>
       <c r="BS16" s="141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT16" s="135">
         <v>45974</v>
@@ -6505,7 +6508,7 @@
         <v>-1.26</v>
       </c>
       <c r="BX16" s="141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY16" s="135">
         <v>45981</v>
@@ -6533,7 +6536,7 @@
       <c r="CZ16" s="19"/>
       <c r="DA16" s="8"/>
       <c r="DB16" s="79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DC16" s="64">
         <f t="shared" si="4"/>
@@ -6586,7 +6589,7 @@
     </row>
     <row r="17" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="28">
         <v>45861</v>
@@ -6601,7 +6604,7 @@
         <v>-1.48</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="28">
         <v>45870</v>
@@ -6616,7 +6619,7 @@
         <v>-1.82</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L17" s="28">
         <v>45883</v>
@@ -6631,7 +6634,7 @@
         <v>-1.36</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="28">
         <v>45889</v>
@@ -6646,7 +6649,7 @@
         <v>-1.36</v>
       </c>
       <c r="U17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V17" s="28">
         <v>45897</v>
@@ -6661,7 +6664,7 @@
         <v>-1.55</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA17" s="28">
         <v>45904</v>
@@ -6676,7 +6679,7 @@
         <v>-1.38</v>
       </c>
       <c r="AE17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF17" s="28">
         <v>45918</v>
@@ -6691,7 +6694,7 @@
         <v>-1.27</v>
       </c>
       <c r="AJ17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK17" s="28">
         <v>45925</v>
@@ -6706,7 +6709,7 @@
         <v>-1.36</v>
       </c>
       <c r="AO17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP17" s="28">
         <v>45932</v>
@@ -6721,7 +6724,7 @@
         <v>-1.21</v>
       </c>
       <c r="AT17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU17" s="28">
         <v>45939</v>
@@ -6736,7 +6739,7 @@
         <v>-1.29</v>
       </c>
       <c r="AY17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ17" s="28">
         <v>45946</v>
@@ -6751,7 +6754,7 @@
         <v>-1.28</v>
       </c>
       <c r="BD17" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE17" s="28">
         <v>45953</v>
@@ -6766,7 +6769,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BI17" s="121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BJ17" s="117">
         <v>45960</v>
@@ -6781,7 +6784,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BN17" s="141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BO17" s="135">
         <v>45967</v>
@@ -6796,7 +6799,7 @@
         <v>-1.39</v>
       </c>
       <c r="BS17" s="141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT17" s="135">
         <v>45974</v>
@@ -6811,7 +6814,7 @@
         <v>-1.49</v>
       </c>
       <c r="BX17" s="141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY17" s="135">
         <v>45981</v>
@@ -6841,7 +6844,7 @@
       <c r="CZ17" s="19"/>
       <c r="DA17" s="8"/>
       <c r="DB17" s="79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="DC17" s="64">
         <f t="shared" si="4"/>
@@ -6894,7 +6897,7 @@
     </row>
     <row r="18" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="28">
         <v>45861</v>
@@ -6909,7 +6912,7 @@
         <v>-1.35</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18" s="28">
         <v>45870</v>
@@ -6924,7 +6927,7 @@
         <v>-1.32</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L18" s="28">
         <v>45883</v>
@@ -6939,7 +6942,7 @@
         <v>-1.46</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="28">
         <v>45889</v>
@@ -6954,7 +6957,7 @@
         <v>-1.27</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V18" s="28">
         <v>45897</v>
@@ -6969,7 +6972,7 @@
         <v>-1.38</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA18" s="28">
         <v>45904</v>
@@ -6984,7 +6987,7 @@
         <v>-1.25</v>
       </c>
       <c r="AE18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF18" s="28">
         <v>45918</v>
@@ -6999,7 +7002,7 @@
         <v>-1.38</v>
       </c>
       <c r="AJ18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK18" s="28">
         <v>45925</v>
@@ -7014,7 +7017,7 @@
         <v>-1.43</v>
       </c>
       <c r="AO18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" s="28">
         <v>45932</v>
@@ -7029,7 +7032,7 @@
         <v>-1.33</v>
       </c>
       <c r="AT18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU18" s="28">
         <v>45939</v>
@@ -7044,7 +7047,7 @@
         <v>-1.39</v>
       </c>
       <c r="AY18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ18" s="28">
         <v>45946</v>
@@ -7059,7 +7062,7 @@
         <v>-1.32</v>
       </c>
       <c r="BD18" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE18" s="28">
         <v>45953</v>
@@ -7074,7 +7077,7 @@
         <v>-1.34</v>
       </c>
       <c r="BI18" s="121" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BJ18" s="117">
         <v>45960</v>
@@ -7119,7 +7122,7 @@
       <c r="CZ18" s="19"/>
       <c r="DA18" s="8"/>
       <c r="DB18" s="79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="DC18" s="64">
         <f t="shared" si="4"/>
@@ -7145,7 +7148,7 @@
     </row>
     <row r="19" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="28">
         <v>45861</v>
@@ -7160,7 +7163,7 @@
         <v>-1.05</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="28">
         <v>45870</v>
@@ -7175,7 +7178,7 @@
         <v>-1.3</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L19" s="28">
         <v>45883</v>
@@ -7190,7 +7193,7 @@
         <v>-1.32</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q19" s="28">
         <v>45889</v>
@@ -7205,7 +7208,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="U19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V19" s="28">
         <v>45897</v>
@@ -7220,7 +7223,7 @@
         <v>-1.32</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA19" s="28">
         <v>45904</v>
@@ -7235,7 +7238,7 @@
         <v>-1.32</v>
       </c>
       <c r="AE19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF19" s="28">
         <v>45918</v>
@@ -7250,7 +7253,7 @@
         <v>-1.39</v>
       </c>
       <c r="AJ19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK19" s="28">
         <v>45925</v>
@@ -7265,7 +7268,7 @@
         <v>-1.32</v>
       </c>
       <c r="AO19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP19" s="28">
         <v>45932</v>
@@ -7280,7 +7283,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AT19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU19" s="28">
         <v>45939</v>
@@ -7295,7 +7298,7 @@
         <v>-1.31</v>
       </c>
       <c r="AY19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" s="28">
         <v>45946</v>
@@ -7310,7 +7313,7 @@
         <v>-1.01</v>
       </c>
       <c r="BD19" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE19" s="28">
         <v>45953</v>
@@ -7325,7 +7328,7 @@
         <v>-1.28</v>
       </c>
       <c r="BI19" s="121" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BJ19" s="117">
         <v>45960</v>
@@ -7340,7 +7343,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BN19" s="141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BO19" s="135">
         <v>45967</v>
@@ -7355,7 +7358,7 @@
         <v>-1.23</v>
       </c>
       <c r="BS19" s="141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BT19" s="135">
         <v>45974</v>
@@ -7370,7 +7373,7 @@
         <v>-1.22</v>
       </c>
       <c r="BX19" s="141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY19" s="135">
         <v>45981</v>
@@ -7399,7 +7402,7 @@
       <c r="CZ19" s="19"/>
       <c r="DA19" s="8"/>
       <c r="DB19" s="79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="DC19" s="64">
         <f t="shared" si="4"/>
@@ -7452,7 +7455,7 @@
     </row>
     <row r="20" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="28">
         <v>45861</v>
@@ -7467,7 +7470,7 @@
         <v>-1.3</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="28">
         <v>45870</v>
@@ -7482,7 +7485,7 @@
         <v>-1.31</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L20" s="28">
         <v>45883</v>
@@ -7497,7 +7500,7 @@
         <v>-1.31</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q20" s="28">
         <v>45889</v>
@@ -7517,7 +7520,7 @@
       <c r="X20" s="27"/>
       <c r="Y20" s="49"/>
       <c r="Z20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA20" s="28">
         <v>45904</v>
@@ -7532,7 +7535,7 @@
         <v>-1.08</v>
       </c>
       <c r="AE20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF20" s="28">
         <v>45918</v>
@@ -7547,7 +7550,7 @@
         <v>-1.32</v>
       </c>
       <c r="AJ20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK20" s="28">
         <v>45925</v>
@@ -7562,7 +7565,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AO20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP20" s="28">
         <v>45932</v>
@@ -7582,7 +7585,7 @@
       <c r="AW20" s="27"/>
       <c r="AX20" s="49"/>
       <c r="AY20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ20" s="28">
         <v>45946</v>
@@ -7597,7 +7600,7 @@
         <v>-1.28</v>
       </c>
       <c r="BD20" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE20" s="28">
         <v>45953</v>
@@ -7612,7 +7615,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BI20" s="121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BJ20" s="117">
         <v>45960</v>
@@ -7627,7 +7630,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BN20" s="141" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BO20" s="135">
         <v>45967</v>
@@ -7642,7 +7645,7 @@
         <v>-1.26</v>
       </c>
       <c r="BS20" s="141" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BT20" s="135">
         <v>45974</v>
@@ -7676,7 +7679,7 @@
       <c r="CZ20" s="19"/>
       <c r="DA20" s="8"/>
       <c r="DB20" s="79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="DC20" s="64">
         <f t="shared" si="4"/>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="21" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="28">
         <v>45861</v>
@@ -7717,7 +7720,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="28">
         <v>45870</v>
@@ -7757,7 +7760,7 @@
       <c r="AH21" s="26"/>
       <c r="AI21" s="40"/>
       <c r="AJ21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21" s="28">
         <v>45925</v>
@@ -7772,7 +7775,7 @@
         <v>-1.2</v>
       </c>
       <c r="AO21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP21" s="28">
         <v>45932</v>
@@ -7787,7 +7790,7 @@
         <v>-1.32</v>
       </c>
       <c r="AT21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU21" s="28">
         <v>45939</v>
@@ -7802,7 +7805,7 @@
         <v>-1.3</v>
       </c>
       <c r="AY21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ21" s="28">
         <v>45946</v>
@@ -7817,7 +7820,7 @@
         <v>-1.2</v>
       </c>
       <c r="BD21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE21" s="28">
         <v>45953</v>
@@ -7867,7 +7870,7 @@
       <c r="CZ21" s="19"/>
       <c r="DA21" s="8"/>
       <c r="DB21" s="79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="DC21" s="64">
         <f t="shared" si="4"/>
@@ -7893,7 +7896,7 @@
     </row>
     <row r="22" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="28">
         <v>45861</v>
@@ -7908,7 +7911,7 @@
         <v>-1.01</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="28">
         <v>45870</v>
@@ -7923,7 +7926,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L22" s="28">
         <v>45883</v>
@@ -7938,7 +7941,7 @@
         <v>-1.19</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="28">
         <v>45889</v>
@@ -7953,7 +7956,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="U22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V22" s="28">
         <v>45897</v>
@@ -7968,7 +7971,7 @@
         <v>-1.32</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA22" s="28">
         <v>45904</v>
@@ -7988,7 +7991,7 @@
       <c r="AH22" s="26"/>
       <c r="AI22" s="40"/>
       <c r="AJ22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK22" s="28">
         <v>45925</v>
@@ -8003,7 +8006,7 @@
         <v>-1.24</v>
       </c>
       <c r="AO22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP22" s="28">
         <v>45932</v>
@@ -8018,7 +8021,7 @@
         <v>-0.9</v>
       </c>
       <c r="AT22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AU22" s="28">
         <v>45939</v>
@@ -8033,7 +8036,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="AY22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AZ22" s="28">
         <v>45946</v>
@@ -8048,7 +8051,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BD22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BE22" s="28">
         <v>45953</v>
@@ -8063,7 +8066,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="BI22" s="121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BJ22" s="117">
         <v>45960</v>
@@ -8078,7 +8081,7 @@
         <v>-1.04</v>
       </c>
       <c r="BN22" s="141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BO22" s="135">
         <v>45967</v>
@@ -8093,7 +8096,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BS22" s="141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BT22" s="135">
         <v>45974</v>
@@ -8108,7 +8111,7 @@
         <v>-1.22</v>
       </c>
       <c r="BX22" s="141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BY22" s="135">
         <v>45981</v>
@@ -8138,7 +8141,7 @@
       <c r="CZ22" s="19"/>
       <c r="DA22" s="8"/>
       <c r="DB22" s="79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="DC22" s="64">
         <f t="shared" si="4"/>
@@ -8191,7 +8194,7 @@
     </row>
     <row r="23" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="28">
         <v>45861</v>
@@ -8206,7 +8209,7 @@
         <v>-1.21</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" s="28">
         <v>45870</v>
@@ -8221,7 +8224,7 @@
         <v>-1.25</v>
       </c>
       <c r="K23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L23" s="28">
         <v>45883</v>
@@ -8236,7 +8239,7 @@
         <v>-1.06</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q23" s="28">
         <v>45889</v>
@@ -8251,7 +8254,7 @@
         <v>-1.17</v>
       </c>
       <c r="U23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V23" s="28">
         <v>45897</v>
@@ -8266,7 +8269,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA23" s="28">
         <v>45904</v>
@@ -8281,7 +8284,7 @@
         <v>-1.26</v>
       </c>
       <c r="AE23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF23" s="28">
         <v>45918</v>
@@ -8296,7 +8299,7 @@
         <v>-1.2</v>
       </c>
       <c r="AJ23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AK23" s="28">
         <v>45925</v>
@@ -8311,7 +8314,7 @@
         <v>-1.32</v>
       </c>
       <c r="AO23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AP23" s="28">
         <v>45932</v>
@@ -8326,7 +8329,7 @@
         <v>-1.07</v>
       </c>
       <c r="AT23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AU23" s="28">
         <v>45939</v>
@@ -8341,7 +8344,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AY23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ23" s="28">
         <v>45946</v>
@@ -8356,7 +8359,7 @@
         <v>-1.07</v>
       </c>
       <c r="BD23" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BE23" s="28">
         <v>45953</v>
@@ -8371,7 +8374,7 @@
         <v>-1.21</v>
       </c>
       <c r="BI23" s="121" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BJ23" s="117">
         <v>45960</v>
@@ -8386,7 +8389,7 @@
         <v>-1.2</v>
       </c>
       <c r="BN23" s="141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BO23" s="135">
         <v>45967</v>
@@ -8401,7 +8404,7 @@
         <v>-1.23</v>
       </c>
       <c r="BS23" s="141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BT23" s="135">
         <v>45974</v>
@@ -8416,7 +8419,7 @@
         <v>-1.34</v>
       </c>
       <c r="BX23" s="141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BY23" s="135">
         <v>45981</v>
@@ -8446,7 +8449,7 @@
       <c r="CZ23" s="19"/>
       <c r="DA23" s="8"/>
       <c r="DB23" s="79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DC23" s="64">
         <f t="shared" si="4"/>
@@ -8499,7 +8502,7 @@
     </row>
     <row r="24" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B24" s="93">
         <v>45870</v>
@@ -8514,7 +8517,7 @@
         <v>-1.62</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G24" s="28">
         <v>45870</v>
@@ -8529,7 +8532,7 @@
         <v>-1.62</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L24" s="28">
         <v>45883</v>
@@ -8544,7 +8547,7 @@
         <v>-1.3</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q24" s="28">
         <v>45889</v>
@@ -8559,7 +8562,7 @@
         <v>-1.61</v>
       </c>
       <c r="U24" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V24" s="28">
         <v>45897</v>
@@ -8574,7 +8577,7 @@
         <v>-1.36</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AA24" s="28">
         <v>45904</v>
@@ -8599,7 +8602,7 @@
       <c r="AM24" s="27"/>
       <c r="AN24" s="49"/>
       <c r="AO24" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AP24" s="28">
         <v>45932</v>
@@ -8664,7 +8667,7 @@
       <c r="CZ24" s="19"/>
       <c r="DA24" s="8"/>
       <c r="DB24" s="79" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="DC24" s="64">
         <f t="shared" si="4"/>
@@ -8690,7 +8693,7 @@
     </row>
     <row r="25" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="28">
         <v>45861</v>
@@ -8705,7 +8708,7 @@
         <v>-1.5</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" s="28">
         <v>45870</v>
@@ -8720,7 +8723,7 @@
         <v>-1.53</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L25" s="28">
         <v>45883</v>
@@ -8735,7 +8738,7 @@
         <v>-1.41</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q25" s="28">
         <v>45889</v>
@@ -8750,7 +8753,7 @@
         <v>-1.28</v>
       </c>
       <c r="U25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V25" s="28">
         <v>45897</v>
@@ -8765,7 +8768,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA25" s="28">
         <v>45904</v>
@@ -8780,7 +8783,7 @@
         <v>-1.48</v>
       </c>
       <c r="AE25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF25" s="28">
         <v>45918</v>
@@ -8795,7 +8798,7 @@
         <v>-1.48</v>
       </c>
       <c r="AJ25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AK25" s="28">
         <v>45925</v>
@@ -8810,7 +8813,7 @@
         <v>-1.45</v>
       </c>
       <c r="AO25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AP25" s="28">
         <v>45932</v>
@@ -8825,7 +8828,7 @@
         <v>-1.49</v>
       </c>
       <c r="AT25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AU25" s="28">
         <v>45939</v>
@@ -8840,7 +8843,7 @@
         <v>-1.37</v>
       </c>
       <c r="AY25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AZ25" s="28">
         <v>45946</v>
@@ -8855,7 +8858,7 @@
         <v>-1.46</v>
       </c>
       <c r="BD25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BE25" s="28">
         <v>45953</v>
@@ -8870,7 +8873,7 @@
         <v>-1.54</v>
       </c>
       <c r="BI25" s="121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BJ25" s="117">
         <v>45960</v>
@@ -8885,7 +8888,7 @@
         <v>-1.51</v>
       </c>
       <c r="BN25" s="141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BO25" s="135">
         <v>45967</v>
@@ -8905,7 +8908,7 @@
       <c r="BV25" s="27"/>
       <c r="BW25" s="49"/>
       <c r="BX25" s="141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BY25" s="135">
         <v>45981</v>
@@ -8934,7 +8937,7 @@
       <c r="CZ25" s="19"/>
       <c r="DA25" s="8"/>
       <c r="DB25" s="79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="DC25" s="64">
         <f t="shared" si="4"/>
@@ -8987,7 +8990,7 @@
     </row>
     <row r="26" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B26" s="93">
         <v>45883</v>
@@ -9007,7 +9010,7 @@
       <c r="I26" s="26"/>
       <c r="J26" s="40"/>
       <c r="K26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L26" s="28">
         <v>45883</v>
@@ -9022,7 +9025,7 @@
         <v>-1.54</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q26" s="28">
         <v>45889</v>
@@ -9037,7 +9040,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="U26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V26" s="28">
         <v>45897</v>
@@ -9052,7 +9055,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AA26" s="28">
         <v>45904</v>
@@ -9067,7 +9070,7 @@
         <v>-1.4</v>
       </c>
       <c r="AE26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AF26" s="28">
         <v>45918</v>
@@ -9082,7 +9085,7 @@
         <v>-1.31</v>
       </c>
       <c r="AJ26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AK26" s="28">
         <v>45925</v>
@@ -9097,7 +9100,7 @@
         <v>-1.21</v>
       </c>
       <c r="AO26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AP26" s="28">
         <v>45932</v>
@@ -9112,7 +9115,7 @@
         <v>-1.17</v>
       </c>
       <c r="AT26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AU26" s="28">
         <v>45939</v>
@@ -9127,7 +9130,7 @@
         <v>-1.21</v>
       </c>
       <c r="AY26" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AZ26" s="28">
         <v>45946</v>
@@ -9147,7 +9150,7 @@
       <c r="BG26" s="27"/>
       <c r="BH26" s="49"/>
       <c r="BI26" s="121" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BJ26" s="117">
         <v>45960</v>
@@ -9192,7 +9195,7 @@
       <c r="CZ26" s="19"/>
       <c r="DA26" s="8"/>
       <c r="DB26" s="79" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="DC26" s="64">
         <f t="shared" si="4"/>
@@ -9218,7 +9221,7 @@
     </row>
     <row r="27" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="28">
         <v>45861</v>
@@ -9238,7 +9241,7 @@
       <c r="I27" s="26"/>
       <c r="J27" s="40"/>
       <c r="K27" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L27" s="28">
         <v>45883</v>
@@ -9253,7 +9256,7 @@
         <v>-1.31</v>
       </c>
       <c r="P27" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q27" s="28">
         <v>45889</v>
@@ -9268,7 +9271,7 @@
         <v>-1.43</v>
       </c>
       <c r="U27" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V27" s="28">
         <v>45897</v>
@@ -9353,7 +9356,7 @@
       <c r="CZ27" s="19"/>
       <c r="DA27" s="8"/>
       <c r="DB27" s="79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="DC27" s="64">
         <f t="shared" si="4"/>
@@ -9379,7 +9382,7 @@
     </row>
     <row r="28" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="B28" s="28">
         <v>45861</v>
@@ -9394,7 +9397,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="F28" s="55" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="G28" s="51">
         <v>45870</v>
@@ -9409,7 +9412,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="L28" s="28">
         <v>45883</v>
@@ -9424,7 +9427,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="Q28" s="28">
         <v>45889</v>
@@ -9439,7 +9442,7 @@
         <v>-1.04</v>
       </c>
       <c r="U28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="V28" s="28">
         <v>45897</v>
@@ -9454,7 +9457,7 @@
         <v>-0.9</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AA28" s="28">
         <v>45904</v>
@@ -9469,7 +9472,7 @@
         <v>-0.84</v>
       </c>
       <c r="AE28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AF28" s="28">
         <v>45918</v>
@@ -9484,7 +9487,7 @@
         <v>-0.94</v>
       </c>
       <c r="AJ28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AK28" s="28">
         <v>45925</v>
@@ -9499,7 +9502,7 @@
         <v>-0.96</v>
       </c>
       <c r="AO28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AP28" s="28">
         <v>45932</v>
@@ -9514,7 +9517,7 @@
         <v>-1.04</v>
       </c>
       <c r="AT28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AU28" s="28">
         <v>45939</v>
@@ -9534,7 +9537,7 @@
       <c r="BB28" s="27"/>
       <c r="BC28" s="49"/>
       <c r="BD28" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BE28" s="28">
         <v>45953</v>
@@ -9549,7 +9552,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BI28" s="121" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BJ28" s="117">
         <v>45960</v>
@@ -9564,7 +9567,7 @@
         <v>-1.08</v>
       </c>
       <c r="BN28" s="141" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BO28" s="135">
         <v>45967</v>
@@ -9579,7 +9582,7 @@
         <v>-1.02</v>
       </c>
       <c r="BS28" s="141" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BT28" s="135">
         <v>45974</v>
@@ -9594,7 +9597,7 @@
         <v>-1.08</v>
       </c>
       <c r="BX28" s="141" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BY28" s="135">
         <v>45980</v>
@@ -9624,7 +9627,7 @@
       <c r="CZ28" s="19"/>
       <c r="DA28" s="8"/>
       <c r="DB28" s="79" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="DC28" s="64">
         <f t="shared" si="4"/>
@@ -9677,7 +9680,7 @@
     </row>
     <row r="29" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="28">
         <v>45861</v>
@@ -9692,7 +9695,7 @@
         <v>-1.52</v>
       </c>
       <c r="F29" s="55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G29" s="51">
         <v>45870</v>
@@ -9707,7 +9710,7 @@
         <v>-1.36</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L29" s="28">
         <v>45883</v>
@@ -9722,7 +9725,7 @@
         <v>-1.33</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q29" s="28">
         <v>45889</v>
@@ -9737,7 +9740,7 @@
         <v>-1.22</v>
       </c>
       <c r="U29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V29" s="28">
         <v>45897</v>
@@ -9752,7 +9755,7 @@
         <v>-1.27</v>
       </c>
       <c r="Z29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA29" s="28">
         <v>45904</v>
@@ -9767,7 +9770,7 @@
         <v>-1.05</v>
       </c>
       <c r="AE29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF29" s="28">
         <v>45918</v>
@@ -9782,7 +9785,7 @@
         <v>-1.21</v>
       </c>
       <c r="AJ29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK29" s="28">
         <v>45925</v>
@@ -9797,7 +9800,7 @@
         <v>-1.33</v>
       </c>
       <c r="AO29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP29" s="28">
         <v>45932</v>
@@ -9812,7 +9815,7 @@
         <v>-1.19</v>
       </c>
       <c r="AT29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AU29" s="28">
         <v>45939</v>
@@ -9832,7 +9835,7 @@
       <c r="BB29" s="27"/>
       <c r="BC29" s="49"/>
       <c r="BD29" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE29" s="28">
         <v>45953</v>
@@ -9847,7 +9850,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="BI29" s="121" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BJ29" s="117">
         <v>45960</v>
@@ -9862,7 +9865,7 @@
         <v>-1.18</v>
       </c>
       <c r="BN29" s="141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BO29" s="135">
         <v>45967</v>
@@ -9877,7 +9880,7 @@
         <v>-1.34</v>
       </c>
       <c r="BS29" s="141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BT29" s="135">
         <v>45974</v>
@@ -9892,7 +9895,7 @@
         <v>-1.17</v>
       </c>
       <c r="BX29" s="141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY29" s="135">
         <v>45981</v>
@@ -9922,7 +9925,7 @@
       <c r="CZ29" s="19"/>
       <c r="DA29" s="8"/>
       <c r="DB29" s="79" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="DC29" s="64">
         <f t="shared" si="4"/>
@@ -10015,7 +10018,7 @@
       <c r="AM30" s="27"/>
       <c r="AN30" s="49"/>
       <c r="AO30" s="30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AP30" s="28">
         <v>45932</v>
@@ -10030,7 +10033,7 @@
         <v>-1.22</v>
       </c>
       <c r="AT30" s="30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AU30" s="28">
         <v>45939</v>
@@ -10050,7 +10053,7 @@
       <c r="BB30" s="27"/>
       <c r="BC30" s="49"/>
       <c r="BD30" s="30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BE30" s="28">
         <v>45953</v>
@@ -10065,7 +10068,7 @@
         <v>-1.24</v>
       </c>
       <c r="BI30" s="121" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BJ30" s="117">
         <v>45960</v>
@@ -10080,7 +10083,7 @@
         <v>-1.21</v>
       </c>
       <c r="BN30" s="141" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BO30" s="135">
         <v>45967</v>
@@ -10095,7 +10098,7 @@
         <v>-1.23</v>
       </c>
       <c r="BS30" s="141" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BT30" s="135">
         <v>45974</v>
@@ -10110,7 +10113,7 @@
         <v>-1.23</v>
       </c>
       <c r="BX30" s="141" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BY30" s="135">
         <v>45981</v>
@@ -10140,7 +10143,7 @@
       <c r="CZ30" s="19"/>
       <c r="DA30" s="8"/>
       <c r="DB30" s="79" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="DC30" s="64">
         <f t="shared" si="4"/>
@@ -10193,7 +10196,7 @@
     </row>
     <row r="31" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B31" s="28">
         <v>45861</v>
@@ -10208,7 +10211,7 @@
         <v>-1.41</v>
       </c>
       <c r="F31" s="55" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G31" s="51">
         <v>45870</v>
@@ -10223,7 +10226,7 @@
         <v>-1.07</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L31" s="28">
         <v>45883</v>
@@ -10238,7 +10241,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="P31" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q31" s="28">
         <v>45889</v>
@@ -10253,7 +10256,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="U31" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V31" s="28">
         <v>45897</v>
@@ -10268,7 +10271,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="Z31" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA31" s="28">
         <v>45904</v>
@@ -10348,7 +10351,7 @@
       <c r="CZ31" s="19"/>
       <c r="DA31" s="8"/>
       <c r="DB31" s="79" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="DC31" s="64">
         <f t="shared" si="4"/>
@@ -10374,7 +10377,7 @@
     </row>
     <row r="32" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B32" s="28">
         <v>45861</v>
@@ -10389,7 +10392,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="F32" s="55" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" s="51">
         <v>45870</v>
@@ -10404,7 +10407,7 @@
         <v>-1.19</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L32" s="28">
         <v>45883</v>
@@ -10419,7 +10422,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="P32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q32" s="28">
         <v>45889</v>
@@ -10434,7 +10437,7 @@
         <v>-1.2</v>
       </c>
       <c r="U32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="V32" s="28">
         <v>45897</v>
@@ -10449,7 +10452,7 @@
         <v>-1.21</v>
       </c>
       <c r="Z32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA32" s="28">
         <v>45904</v>
@@ -10464,7 +10467,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AE32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF32" s="28">
         <v>45918</v>
@@ -10479,7 +10482,7 @@
         <v>-1.05</v>
       </c>
       <c r="AJ32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK32" s="28">
         <v>45925</v>
@@ -10549,7 +10552,7 @@
       <c r="CZ32" s="19"/>
       <c r="DA32" s="8"/>
       <c r="DB32" s="79" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="DC32" s="64">
         <f t="shared" si="4"/>
@@ -10575,7 +10578,7 @@
     </row>
     <row r="33" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="28">
         <v>45861</v>
@@ -10590,7 +10593,7 @@
         <v>-1.27</v>
       </c>
       <c r="F33" s="55" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G33" s="51">
         <v>45870</v>
@@ -10605,7 +10608,7 @@
         <v>-1.33</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L33" s="28">
         <v>45883</v>
@@ -10620,7 +10623,7 @@
         <v>-1.36</v>
       </c>
       <c r="P33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q33" s="28">
         <v>45889</v>
@@ -10635,7 +10638,7 @@
         <v>-1.19</v>
       </c>
       <c r="U33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="V33" s="28">
         <v>45897</v>
@@ -10650,7 +10653,7 @@
         <v>-1.21</v>
       </c>
       <c r="Z33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AA33" s="28">
         <v>45904</v>
@@ -10665,7 +10668,7 @@
         <v>-1.19</v>
       </c>
       <c r="AE33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AF33" s="28">
         <v>45918</v>
@@ -10680,7 +10683,7 @@
         <v>-1.19</v>
       </c>
       <c r="AJ33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AK33" s="28">
         <v>45925</v>
@@ -10695,7 +10698,7 @@
         <v>-1.26</v>
       </c>
       <c r="AO33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AP33" s="28">
         <v>45932</v>
@@ -10710,7 +10713,7 @@
         <v>-1.25</v>
       </c>
       <c r="AT33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AU33" s="28">
         <v>45939</v>
@@ -10725,7 +10728,7 @@
         <v>-1.34</v>
       </c>
       <c r="AY33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AZ33" s="28">
         <v>45946</v>
@@ -10740,7 +10743,7 @@
         <v>-1.3</v>
       </c>
       <c r="BD33" s="30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BE33" s="28">
         <v>45953</v>
@@ -10755,7 +10758,7 @@
         <v>-1.32</v>
       </c>
       <c r="BI33" s="121" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BJ33" s="117">
         <v>45960</v>
@@ -10770,7 +10773,7 @@
         <v>-1.4</v>
       </c>
       <c r="BN33" s="141" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BO33" s="135">
         <v>45967</v>
@@ -10785,7 +10788,7 @@
         <v>-1.27</v>
       </c>
       <c r="BS33" s="141" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BT33" s="135">
         <v>45974</v>
@@ -10820,7 +10823,7 @@
       <c r="CZ33" s="19"/>
       <c r="DA33" s="8"/>
       <c r="DB33" s="79" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="DC33" s="64">
         <f t="shared" si="4"/>
@@ -10846,7 +10849,7 @@
     </row>
     <row r="34" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" s="28">
         <v>45861</v>
@@ -10861,7 +10864,7 @@
         <v>-1.46</v>
       </c>
       <c r="F34" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G34" s="51">
         <v>45870</v>
@@ -10876,7 +10879,7 @@
         <v>-1.46</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L34" s="28">
         <v>45883</v>
@@ -10891,7 +10894,7 @@
         <v>-1.42</v>
       </c>
       <c r="P34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q34" s="28">
         <v>45889</v>
@@ -10906,7 +10909,7 @@
         <v>-1.41</v>
       </c>
       <c r="U34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="V34" s="28">
         <v>45897</v>
@@ -10921,7 +10924,7 @@
         <v>-1.35</v>
       </c>
       <c r="Z34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA34" s="28">
         <v>45904</v>
@@ -10936,7 +10939,7 @@
         <v>-1.42</v>
       </c>
       <c r="AE34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF34" s="28">
         <v>45918</v>
@@ -10956,7 +10959,7 @@
       <c r="AM34" s="27"/>
       <c r="AN34" s="49"/>
       <c r="AO34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP34" s="28">
         <v>45932</v>
@@ -10971,7 +10974,7 @@
         <v>-1.32</v>
       </c>
       <c r="AT34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AU34" s="28">
         <v>45939</v>
@@ -10986,7 +10989,7 @@
         <v>-1.38</v>
       </c>
       <c r="AY34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AZ34" s="28">
         <v>45946</v>
@@ -11001,7 +11004,7 @@
         <v>-1.41</v>
       </c>
       <c r="BD34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE34" s="28">
         <v>45953</v>
@@ -11016,7 +11019,7 @@
         <v>-1.39</v>
       </c>
       <c r="BI34" s="121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BJ34" s="117">
         <v>45960</v>
@@ -11031,7 +11034,7 @@
         <v>-1.28</v>
       </c>
       <c r="BN34" s="129" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BO34" s="135">
         <v>45967</v>
@@ -11046,7 +11049,7 @@
         <v>-1.36</v>
       </c>
       <c r="BS34" s="141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BT34" s="135">
         <v>45974</v>
@@ -11061,7 +11064,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BX34" s="141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY34" s="135">
         <v>45981</v>
@@ -11086,7 +11089,7 @@
       <c r="CZ34" s="19"/>
       <c r="DA34" s="8"/>
       <c r="DB34" s="79" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="DC34" s="64">
         <f t="shared" si="4"/>
@@ -11139,7 +11142,7 @@
     </row>
     <row r="35" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B35" s="28">
         <v>45861</v>
@@ -11159,7 +11162,7 @@
       <c r="I35" s="26"/>
       <c r="J35" s="40"/>
       <c r="K35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L35" s="28">
         <v>45883</v>
@@ -11174,7 +11177,7 @@
         <v>-1</v>
       </c>
       <c r="P35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q35" s="28">
         <v>45889</v>
@@ -11189,7 +11192,7 @@
         <v>-0.99</v>
       </c>
       <c r="U35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V35" s="28">
         <v>45897</v>
@@ -11204,7 +11207,7 @@
         <v>-1.03</v>
       </c>
       <c r="Z35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA35" s="28">
         <v>45904</v>
@@ -11219,7 +11222,7 @@
         <v>-0.99</v>
       </c>
       <c r="AE35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF35" s="28">
         <v>45918</v>
@@ -11234,7 +11237,7 @@
         <v>-1.08</v>
       </c>
       <c r="AJ35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK35" s="28">
         <v>45925</v>
@@ -11249,7 +11252,7 @@
         <v>-1</v>
       </c>
       <c r="AO35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AP35" s="28">
         <v>45932</v>
@@ -11264,7 +11267,7 @@
         <v>-1.01</v>
       </c>
       <c r="AT35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU35" s="28">
         <v>45939</v>
@@ -11279,7 +11282,7 @@
         <v>-0.91</v>
       </c>
       <c r="AY35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ35" s="28">
         <v>45946</v>
@@ -11294,7 +11297,7 @@
         <v>-0.93</v>
       </c>
       <c r="BD35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE35" s="28">
         <v>45953</v>
@@ -11309,7 +11312,7 @@
         <v>-0.77</v>
       </c>
       <c r="BI35" s="121" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BJ35" s="117">
         <v>45960</v>
@@ -11324,7 +11327,7 @@
         <v>-1.03</v>
       </c>
       <c r="BN35" s="141" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO35" s="135">
         <v>45967</v>
@@ -11339,7 +11342,7 @@
         <v>-1</v>
       </c>
       <c r="BS35" s="141" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BT35" s="135">
         <v>45974</v>
@@ -11354,7 +11357,7 @@
         <v>-0.87</v>
       </c>
       <c r="BX35" s="141" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BY35" s="135">
         <v>45981</v>
@@ -11378,7 +11381,7 @@
       <c r="CV35" s="18"/>
       <c r="CZ35" s="19"/>
       <c r="DB35" s="79" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="DC35" s="64">
         <f t="shared" si="4"/>
@@ -11431,7 +11434,7 @@
     </row>
     <row r="36" spans="1:118" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B36" s="28">
         <v>45855</v>
@@ -11486,7 +11489,7 @@
       <c r="AR36" s="27"/>
       <c r="AS36" s="49"/>
       <c r="AT36" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AU36" s="28">
         <v>45939</v>
@@ -11501,7 +11504,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AY36" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AZ36" s="28">
         <v>45946</v>
@@ -11516,7 +11519,7 @@
         <v>-1.33</v>
       </c>
       <c r="BD36" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BE36" s="28">
         <v>45953</v>
@@ -11531,7 +11534,7 @@
         <v>-1.17</v>
       </c>
       <c r="BI36" s="121" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BJ36" s="117">
         <v>45960</v>
@@ -11546,7 +11549,7 @@
         <v>-1.28</v>
       </c>
       <c r="BN36" s="141" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BO36" s="135">
         <v>45967</v>
@@ -11561,7 +11564,7 @@
         <v>-1.2</v>
       </c>
       <c r="BS36" s="141" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BT36" s="135">
         <v>45974</v>
@@ -11576,7 +11579,7 @@
         <v>-1.01</v>
       </c>
       <c r="BX36" s="141" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BY36" s="135">
         <v>45981</v>
@@ -11615,7 +11618,7 @@
       <c r="CY36" s="23"/>
       <c r="CZ36" s="24"/>
       <c r="DB36" s="79" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="DC36" s="64">
         <f t="shared" si="4"/>
@@ -11668,7 +11671,7 @@
     </row>
     <row r="37" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="93">
         <v>45883</v>
@@ -11688,7 +11691,7 @@
       <c r="I37" s="26"/>
       <c r="J37" s="40"/>
       <c r="K37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L37" s="28">
         <v>45883</v>
@@ -11703,7 +11706,7 @@
         <v>-0.86</v>
       </c>
       <c r="P37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q37" s="28">
         <v>45889</v>
@@ -11718,7 +11721,7 @@
         <v>-1.04</v>
       </c>
       <c r="U37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V37" s="28">
         <v>45897</v>
@@ -11733,7 +11736,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="Z37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AA37" s="28">
         <v>45904</v>
@@ -11748,7 +11751,7 @@
         <v>-1.01</v>
       </c>
       <c r="AE37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AF37" s="28">
         <v>45918</v>
@@ -11763,7 +11766,7 @@
         <v>-1.07</v>
       </c>
       <c r="AJ37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AK37" s="28">
         <v>45925</v>
@@ -11778,7 +11781,7 @@
         <v>-1.01</v>
       </c>
       <c r="AO37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AP37" s="28">
         <v>45932</v>
@@ -11793,7 +11796,7 @@
         <v>-1.05</v>
       </c>
       <c r="AT37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AU37" s="28">
         <v>45939</v>
@@ -11808,7 +11811,7 @@
         <v>-0.87</v>
       </c>
       <c r="AY37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AZ37" s="28">
         <v>45946</v>
@@ -11823,7 +11826,7 @@
         <v>-1.02</v>
       </c>
       <c r="BD37" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BE37" s="28">
         <v>45953</v>
@@ -11838,7 +11841,7 @@
         <v>-0.95</v>
       </c>
       <c r="BI37" s="121" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BJ37" s="117">
         <v>45960</v>
@@ -11853,7 +11856,7 @@
         <v>-0.84</v>
       </c>
       <c r="BN37" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BO37" s="135">
         <v>45967</v>
@@ -11868,7 +11871,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="BS37" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BT37" s="135">
         <v>45974</v>
@@ -11883,7 +11886,7 @@
         <v>-1.06</v>
       </c>
       <c r="BX37" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BY37" s="135">
         <v>45981</v>
@@ -11898,7 +11901,7 @@
         <v>-1.02</v>
       </c>
       <c r="DB37" s="79" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="DC37" s="64">
         <f t="shared" si="4"/>
@@ -11951,7 +11954,7 @@
     </row>
     <row r="38" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" s="93">
         <v>45883</v>
@@ -11971,7 +11974,7 @@
       <c r="I38" s="26"/>
       <c r="J38" s="40"/>
       <c r="K38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L38" s="28">
         <v>45883</v>
@@ -11986,7 +11989,7 @@
         <v>-1.23</v>
       </c>
       <c r="P38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q38" s="28">
         <v>45889</v>
@@ -12001,7 +12004,7 @@
         <v>-1.18</v>
       </c>
       <c r="U38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V38" s="28">
         <v>45897</v>
@@ -12016,7 +12019,7 @@
         <v>-1.26</v>
       </c>
       <c r="Z38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA38" s="28">
         <v>45904</v>
@@ -12031,7 +12034,7 @@
         <v>-1.06</v>
       </c>
       <c r="AE38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF38" s="28">
         <v>45918</v>
@@ -12046,7 +12049,7 @@
         <v>-1.28</v>
       </c>
       <c r="AJ38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK38" s="28">
         <v>45925</v>
@@ -12061,7 +12064,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AO38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AP38" s="28">
         <v>45932</v>
@@ -12076,7 +12079,7 @@
         <v>-1.25</v>
       </c>
       <c r="AT38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AU38" s="28">
         <v>45939</v>
@@ -12091,7 +12094,7 @@
         <v>-1.25</v>
       </c>
       <c r="AY38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AZ38" s="28">
         <v>45946</v>
@@ -12106,7 +12109,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BD38" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BE38" s="28">
         <v>45953</v>
@@ -12121,7 +12124,7 @@
         <v>-1.08</v>
       </c>
       <c r="BI38" s="121" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BJ38" s="117">
         <v>45960</v>
@@ -12136,7 +12139,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BN38" s="141" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BO38" s="135">
         <v>45967</v>
@@ -12151,7 +12154,7 @@
         <v>-1.28</v>
       </c>
       <c r="BS38" s="141" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BT38" s="135">
         <v>45974</v>
@@ -12166,7 +12169,7 @@
         <v>-1.18</v>
       </c>
       <c r="BX38" s="141" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BY38" s="135">
         <v>45981</v>
@@ -12181,7 +12184,7 @@
         <v>-1.18</v>
       </c>
       <c r="DB38" s="79" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="DC38" s="64">
         <f t="shared" si="4"/>
@@ -12234,7 +12237,7 @@
     </row>
     <row r="39" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="28">
         <v>45861</v>
@@ -12249,7 +12252,7 @@
         <v>-1.2</v>
       </c>
       <c r="F39" s="55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G39" s="51">
         <v>45870</v>
@@ -12264,7 +12267,7 @@
         <v>-1.33</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L39" s="28">
         <v>45883</v>
@@ -12279,7 +12282,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="P39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q39" s="28">
         <v>45889</v>
@@ -12294,7 +12297,7 @@
         <v>-1.21</v>
       </c>
       <c r="U39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V39" s="28">
         <v>45897</v>
@@ -12309,7 +12312,7 @@
         <v>-1.17</v>
       </c>
       <c r="Z39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA39" s="28">
         <v>45904</v>
@@ -12324,7 +12327,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AE39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF39" s="28">
         <v>45918</v>
@@ -12339,7 +12342,7 @@
         <v>-1.22</v>
       </c>
       <c r="AJ39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK39" s="28">
         <v>45925</v>
@@ -12354,7 +12357,7 @@
         <v>-1.23</v>
       </c>
       <c r="AO39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP39" s="28">
         <v>45932</v>
@@ -12369,7 +12372,7 @@
         <v>-1.29</v>
       </c>
       <c r="AT39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AU39" s="28">
         <v>45939</v>
@@ -12384,7 +12387,7 @@
         <v>-1.17</v>
       </c>
       <c r="AY39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AZ39" s="28">
         <v>45946</v>
@@ -12399,7 +12402,7 @@
         <v>-1.36</v>
       </c>
       <c r="BD39" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE39" s="28">
         <v>45953</v>
@@ -12414,7 +12417,7 @@
         <v>-1.19</v>
       </c>
       <c r="BI39" s="121" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BJ39" s="117">
         <v>45960</v>
@@ -12429,7 +12432,7 @@
         <v>-1.02</v>
       </c>
       <c r="BN39" s="141" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BO39" s="135">
         <v>45967</v>
@@ -12444,7 +12447,7 @@
         <v>-1.22</v>
       </c>
       <c r="BS39" s="141" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BT39" s="135">
         <v>45974</v>
@@ -12459,7 +12462,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="BX39" s="141" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY39" s="135">
         <v>45981</v>
@@ -12474,7 +12477,7 @@
         <v>-1.08</v>
       </c>
       <c r="DB39" s="79" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="DC39" s="64">
         <f t="shared" si="4"/>
@@ -12527,7 +12530,7 @@
     </row>
     <row r="40" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="28">
         <v>45861</v>
@@ -12542,7 +12545,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="F40" s="55" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G40" s="51">
         <v>45870</v>
@@ -12557,7 +12560,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L40" s="28">
         <v>45883</v>
@@ -12572,7 +12575,7 @@
         <v>-1.08</v>
       </c>
       <c r="P40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q40" s="28">
         <v>45889</v>
@@ -12587,7 +12590,7 @@
         <v>-1.26</v>
       </c>
       <c r="U40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V40" s="28">
         <v>45897</v>
@@ -12622,7 +12625,7 @@
       <c r="AR40" s="27"/>
       <c r="AS40" s="49"/>
       <c r="AT40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AU40" s="28">
         <v>45939</v>
@@ -12637,7 +12640,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="AY40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AZ40" s="28">
         <v>45946</v>
@@ -12652,7 +12655,7 @@
         <v>-1.34</v>
       </c>
       <c r="BD40" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BE40" s="28">
         <v>45953</v>
@@ -12672,7 +12675,7 @@
       <c r="BL40" s="52"/>
       <c r="BM40" s="76"/>
       <c r="BN40" s="141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BO40" s="135">
         <v>45967</v>
@@ -12687,7 +12690,7 @@
         <v>-1.24</v>
       </c>
       <c r="BS40" s="141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BT40" s="135">
         <v>45974</v>
@@ -12702,7 +12705,7 @@
         <v>-1.38</v>
       </c>
       <c r="BX40" s="141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BY40" s="135">
         <v>45981</v>
@@ -12717,7 +12720,7 @@
         <v>-1.39</v>
       </c>
       <c r="DB40" s="79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="DC40" s="64">
         <f t="shared" si="4"/>
@@ -12770,7 +12773,7 @@
     </row>
     <row r="41" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="28">
         <v>45861</v>
@@ -12785,7 +12788,7 @@
         <v>-0.93</v>
       </c>
       <c r="F41" s="55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G41" s="51">
         <v>45870</v>
@@ -12800,7 +12803,7 @@
         <v>-0.91</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L41" s="28">
         <v>45883</v>
@@ -12815,7 +12818,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="P41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q41" s="28">
         <v>45889</v>
@@ -12830,7 +12833,7 @@
         <v>-1.18</v>
       </c>
       <c r="U41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V41" s="28">
         <v>45897</v>
@@ -12845,7 +12848,7 @@
         <v>-1.41</v>
       </c>
       <c r="Z41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA41" s="28">
         <v>45904</v>
@@ -12880,7 +12883,7 @@
       <c r="AW41" s="27"/>
       <c r="AX41" s="49"/>
       <c r="AY41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AZ41" s="28">
         <v>45946</v>
@@ -12895,7 +12898,7 @@
         <v>-0.83</v>
       </c>
       <c r="BD41" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE41" s="28">
         <v>45953</v>
@@ -12910,7 +12913,7 @@
         <v>-1.06</v>
       </c>
       <c r="BI41" s="121" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BJ41" s="117">
         <v>45960</v>
@@ -12925,7 +12928,7 @@
         <v>-0.96</v>
       </c>
       <c r="BN41" s="141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BO41" s="135">
         <v>45967</v>
@@ -12940,7 +12943,7 @@
         <v>-1.37</v>
       </c>
       <c r="BS41" s="141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BT41" s="135">
         <v>45974</v>
@@ -12955,7 +12958,7 @@
         <v>-1.32</v>
       </c>
       <c r="BX41" s="141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY41" s="135">
         <v>45981</v>
@@ -12970,7 +12973,7 @@
         <v>-1.19</v>
       </c>
       <c r="DB41" s="79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="DC41" s="64">
         <f t="shared" si="4"/>
@@ -13023,7 +13026,7 @@
     </row>
     <row r="42" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="28">
         <v>45861</v>
@@ -13038,7 +13041,7 @@
         <v>-1.45</v>
       </c>
       <c r="F42" s="55" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G42" s="51">
         <v>45870</v>
@@ -13053,7 +13056,7 @@
         <v>-1.42</v>
       </c>
       <c r="K42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L42" s="28">
         <v>45883</v>
@@ -13068,7 +13071,7 @@
         <v>-1.29</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q42" s="28">
         <v>45889</v>
@@ -13083,7 +13086,7 @@
         <v>-1.28</v>
       </c>
       <c r="U42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V42" s="28">
         <v>45897</v>
@@ -13098,7 +13101,7 @@
         <v>-1.17</v>
       </c>
       <c r="Z42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA42" s="28">
         <v>45904</v>
@@ -13113,7 +13116,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="AE42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AF42" s="28">
         <v>45918</v>
@@ -13128,7 +13131,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AJ42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK42" s="28">
         <v>45925</v>
@@ -13143,7 +13146,7 @@
         <v>-1.05</v>
       </c>
       <c r="AO42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AP42" s="28">
         <v>45932</v>
@@ -13158,7 +13161,7 @@
         <v>-0.96</v>
       </c>
       <c r="AT42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AU42" s="28">
         <v>45939</v>
@@ -13173,7 +13176,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AY42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AZ42" s="28">
         <v>45946</v>
@@ -13188,7 +13191,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="BD42" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BE42" s="28">
         <v>45953</v>
@@ -13203,7 +13206,7 @@
         <v>-1.18</v>
       </c>
       <c r="BI42" s="121" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BJ42" s="117">
         <v>45960</v>
@@ -13218,7 +13221,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="BN42" s="141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BO42" s="135">
         <v>45967</v>
@@ -13233,7 +13236,7 @@
         <v>-1.21</v>
       </c>
       <c r="BS42" s="141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BT42" s="135">
         <v>45974</v>
@@ -13248,7 +13251,7 @@
         <v>-1.06</v>
       </c>
       <c r="BX42" s="141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BY42" s="135">
         <v>45981</v>
@@ -13263,7 +13266,7 @@
         <v>-0.98</v>
       </c>
       <c r="DB42" s="79" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="DC42" s="64">
         <f t="shared" si="4"/>
@@ -13316,7 +13319,7 @@
     </row>
     <row r="43" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B43" s="93">
         <v>45883</v>
@@ -13376,7 +13379,7 @@
       <c r="AW43" s="27"/>
       <c r="AX43" s="49"/>
       <c r="AY43" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AZ43" s="28">
         <v>45946</v>
@@ -13391,7 +13394,7 @@
         <v>-1.63</v>
       </c>
       <c r="BD43" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BE43" s="28">
         <v>45953</v>
@@ -13406,7 +13409,7 @@
         <v>-1.35</v>
       </c>
       <c r="BI43" s="121" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BJ43" s="117">
         <v>45960</v>
@@ -13421,7 +13424,7 @@
         <v>-1.31</v>
       </c>
       <c r="BN43" s="141" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BO43" s="135">
         <v>45967</v>
@@ -13436,7 +13439,7 @@
         <v>-1.28</v>
       </c>
       <c r="BS43" s="141" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BT43" s="135">
         <v>45974</v>
@@ -13456,7 +13459,7 @@
       <c r="CA43" s="27"/>
       <c r="CB43" s="31"/>
       <c r="DB43" s="79" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="DC43" s="64">
         <f t="shared" si="4"/>
@@ -13482,7 +13485,7 @@
     </row>
     <row r="44" spans="1:118" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B44" s="28">
         <v>45861</v>
@@ -13497,7 +13500,7 @@
         <v>-1.38</v>
       </c>
       <c r="F44" s="55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G44" s="51">
         <v>45870</v>
@@ -13512,7 +13515,7 @@
         <v>-1.21</v>
       </c>
       <c r="K44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L44" s="28">
         <v>45883</v>
@@ -13527,7 +13530,7 @@
         <v>-1.23</v>
       </c>
       <c r="P44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q44" s="28">
         <v>45889</v>
@@ -13542,7 +13545,7 @@
         <v>-1.29</v>
       </c>
       <c r="U44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="V44" s="28">
         <v>45897</v>
@@ -13557,7 +13560,7 @@
         <v>-1.4</v>
       </c>
       <c r="Z44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA44" s="28">
         <v>45904</v>
@@ -13572,7 +13575,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="AE44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF44" s="28">
         <v>45918</v>
@@ -13587,7 +13590,7 @@
         <v>-1.23</v>
       </c>
       <c r="AJ44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK44" s="28">
         <v>45925</v>
@@ -13602,7 +13605,7 @@
         <v>-1.24</v>
       </c>
       <c r="AO44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP44" s="28">
         <v>45932</v>
@@ -13617,7 +13620,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="AT44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AU44" s="28">
         <v>45939</v>
@@ -13632,7 +13635,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="AY44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AZ44" s="28">
         <v>45946</v>
@@ -13647,7 +13650,7 @@
         <v>-1.26</v>
       </c>
       <c r="BD44" s="30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE44" s="28">
         <v>45953</v>
@@ -13662,7 +13665,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="BI44" s="121" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BJ44" s="117">
         <v>45960</v>
@@ -13677,7 +13680,7 @@
         <v>-1.03</v>
       </c>
       <c r="BN44" s="141" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BO44" s="135">
         <v>45967</v>
@@ -13692,7 +13695,7 @@
         <v>-1.02</v>
       </c>
       <c r="BS44" s="141" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BT44" s="135">
         <v>45974</v>
@@ -13707,7 +13710,7 @@
         <v>-1.05</v>
       </c>
       <c r="BX44" s="141" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY44" s="135">
         <v>45981</v>
@@ -13722,7 +13725,7 @@
         <v>-1.05</v>
       </c>
       <c r="DB44" s="79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="DC44" s="64">
         <f t="shared" si="4"/>
@@ -13775,7 +13778,7 @@
     </row>
     <row r="45" spans="1:118" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B45" s="44">
         <v>45861</v>
@@ -13790,7 +13793,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="F45" s="56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G45" s="57">
         <v>45870</v>
@@ -13805,7 +13808,7 @@
         <v>-1.4</v>
       </c>
       <c r="K45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L45" s="44">
         <v>45883</v>
@@ -13820,7 +13823,7 @@
         <v>-1.22</v>
       </c>
       <c r="P45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q45" s="44">
         <v>45889</v>
@@ -13835,7 +13838,7 @@
         <v>-1.23</v>
       </c>
       <c r="U45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="V45" s="44">
         <v>45897</v>
@@ -13850,7 +13853,7 @@
         <v>-1.27</v>
       </c>
       <c r="Z45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA45" s="44">
         <v>45904</v>
@@ -13865,7 +13868,7 @@
         <v>-1.01</v>
       </c>
       <c r="AE45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF45" s="44">
         <v>45918</v>
@@ -13880,7 +13883,7 @@
         <v>-1.21</v>
       </c>
       <c r="AJ45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AK45" s="44">
         <v>45925</v>
@@ -13895,7 +13898,7 @@
         <v>-1.3</v>
       </c>
       <c r="AO45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AP45" s="44">
         <v>45932</v>
@@ -13910,7 +13913,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="AT45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AU45" s="44">
         <v>45939</v>
@@ -13925,7 +13928,7 @@
         <v>-0.83</v>
       </c>
       <c r="AY45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AZ45" s="44">
         <v>45946</v>
@@ -13940,7 +13943,7 @@
         <v>-1.23</v>
       </c>
       <c r="BD45" s="43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BE45" s="44">
         <v>45953</v>
@@ -13955,7 +13958,7 @@
         <v>-1.24</v>
       </c>
       <c r="BI45" s="123" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BJ45" s="124">
         <v>45960</v>
@@ -13970,7 +13973,7 @@
         <v>-0.81</v>
       </c>
       <c r="BN45" s="143" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BO45" s="144">
         <v>45967</v>
@@ -13985,7 +13988,7 @@
         <v>-1.05</v>
       </c>
       <c r="BS45" s="143" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BT45" s="144">
         <v>45974</v>
@@ -14000,7 +14003,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="BX45" s="143" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="BY45" s="144">
         <v>45981</v>
@@ -14015,7 +14018,7 @@
         <v>-0.99</v>
       </c>
       <c r="DB45" s="80" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="DC45" s="114">
         <f t="shared" si="4"/>
@@ -14068,7 +14071,7 @@
     </row>
     <row r="46" spans="1:118" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="4">
         <f>AVERAGE(C2:C45)</f>
@@ -14083,7 +14086,7 @@
         <v>-1.3006976744186047</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H46" s="4">
         <f>AVERAGE(H2:H45)</f>
@@ -14098,7 +14101,7 @@
         <v>-1.3162499999999999</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M46" s="4">
         <f>AVERAGE(M2:M45)</f>
@@ -14113,7 +14116,7 @@
         <v>-1.2421052631578944</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R46" s="4">
         <f>AVERAGE(R2:R45)</f>
@@ -14128,7 +14131,7 @@
         <v>-1.2642105263157892</v>
       </c>
       <c r="U46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="W46" s="4">
         <f>AVERAGE(W2:W45)</f>
@@ -14143,7 +14146,7 @@
         <v>-1.2427027027027029</v>
       </c>
       <c r="Z46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA46"/>
       <c r="AB46" s="4">
@@ -14159,7 +14162,7 @@
         <v>-1.208</v>
       </c>
       <c r="AE46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG46" s="4">
         <f>AVERAGE(AG2:AG45)</f>
@@ -14174,7 +14177,7 @@
         <v>-1.2340000000000002</v>
       </c>
       <c r="AJ46" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK46"/>
       <c r="AL46" s="4">
@@ -14190,7 +14193,7 @@
         <v>-1.2335294117647055</v>
       </c>
       <c r="AO46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AQ46" s="4">
         <f>AVERAGE(AQ2:AQ45)</f>
@@ -14205,7 +14208,7 @@
         <v>-1.2255555555555551</v>
       </c>
       <c r="AT46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AV46" s="4">
         <f>AVERAGE(AV2:AV45)</f>
@@ -14220,7 +14223,7 @@
         <v>-1.2066666666666668</v>
       </c>
       <c r="AY46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BA46" s="4">
         <f>AVERAGE(BA2:BA45)</f>
@@ -14235,7 +14238,7 @@
         <v>-1.2403030303030302</v>
       </c>
       <c r="BD46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF46" s="4">
         <f>AVERAGE(BF2:BF45)</f>
@@ -14250,7 +14253,7 @@
         <v>-1.2145714285714286</v>
       </c>
       <c r="BI46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BJ46" s="12"/>
       <c r="BK46" s="4">
@@ -14266,7 +14269,7 @@
         <v>-1.1916666666666673</v>
       </c>
       <c r="BN46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BP46" s="4">
         <f>AVERAGE(BP2:BP45)</f>
@@ -14281,7 +14284,7 @@
         <v>-1.233529411764706</v>
       </c>
       <c r="BS46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU46" s="4">
         <f>AVERAGE(BU2:BU45)</f>
@@ -14296,7 +14299,7 @@
         <v>-1.1890625000000001</v>
       </c>
       <c r="BX46" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BZ46" s="4">
         <f>AVERAGE(BZ2:BZ45)</f>
@@ -14311,17 +14314,17 @@
         <v>-1.1720689655172414</v>
       </c>
       <c r="DB46" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="DC46" s="157">
+        <v>48</v>
+      </c>
+      <c r="DC46" s="155">
         <f t="shared" si="4"/>
         <v>0.87495894534787655</v>
       </c>
-      <c r="DD46" s="158">
+      <c r="DD46" s="156">
         <f t="shared" si="5"/>
         <v>39.583072229262903</v>
       </c>
-      <c r="DE46" s="160">
+      <c r="DE46" s="158">
         <f t="shared" si="6"/>
         <v>-1.232182487712812</v>
       </c>
@@ -14363,6 +14366,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:CB46" xr:uid="{95BE8E96-3062-E445-B64D-7D9F0059CEAD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="BX2:CB30">
     <sortCondition ref="BX2:BX30"/>
   </sortState>
@@ -14490,271 +14494,271 @@
         <v>8</v>
       </c>
       <c r="B1" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="E1" s="39" t="s">
         <v>53</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>55</v>
       </c>
       <c r="F1" s="46" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="J1" s="66" t="s">
         <v>53</v>
-      </c>
-      <c r="I1" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1" s="66" t="s">
-        <v>55</v>
       </c>
       <c r="K1" s="46" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="47" t="s">
+      <c r="O1" s="48" t="s">
         <v>53</v>
-      </c>
-      <c r="N1" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>55</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="Q1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AK1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AP1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AU1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AZ1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BE1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BG1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="BI1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BJ1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="BN1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BO1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="BS1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="BT1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="BU1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="BV1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="BU1" s="15" t="s">
+      <c r="BW1" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="BV1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="BW1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="BX1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="BY1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="BZ1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="CA1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="BZ1" s="15" t="s">
+      <c r="CB1" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="CA1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="CB1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="CC1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="CD1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="CE1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="CE1" s="15" t="s">
+      <c r="CG1" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="CF1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="CG1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="CH1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="CI1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="CJ1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="CK1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="CJ1" s="15" t="s">
+      <c r="CL1" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="CK1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="CL1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="CM1" s="14"/>
       <c r="CN1" s="14"/>
@@ -14872,7 +14876,7 @@
         <v>411.25</v>
       </c>
       <c r="Y2" s="90" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Z2" s="53" t="s">
         <v>13</v>
@@ -15729,7 +15733,7 @@
         <v>412.25</v>
       </c>
       <c r="T5" s="82" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U5" s="35" t="s">
         <v>16</v>
@@ -16289,7 +16293,7 @@
     </row>
     <row r="7" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A7" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B7" s="86">
         <v>45874</v>
@@ -16309,7 +16313,7 @@
       <c r="I7" s="27"/>
       <c r="J7" s="49"/>
       <c r="K7" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L7" s="28">
         <v>45874</v>
@@ -16324,7 +16328,7 @@
         <v>-9.0267983074753104</v>
       </c>
       <c r="P7" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="28">
         <v>45880</v>
@@ -16339,7 +16343,7 @@
         <v>-4.6161565479177096</v>
       </c>
       <c r="U7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V7" s="32">
         <v>45886</v>
@@ -16354,7 +16358,7 @@
         <v>-8.90316659017898</v>
       </c>
       <c r="Z7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AA7" s="32">
         <v>45894</v>
@@ -16369,7 +16373,7 @@
         <v>-6.5671641791044699</v>
       </c>
       <c r="AE7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AF7" s="32">
         <v>45901</v>
@@ -16384,7 +16388,7 @@
         <v>-6.3407550822846099</v>
       </c>
       <c r="AJ7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK7" s="32">
         <v>45908</v>
@@ -16399,7 +16403,7 @@
         <v>-4.1604010025062603</v>
       </c>
       <c r="AO7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AP7" s="32">
         <v>45915</v>
@@ -16414,7 +16418,7 @@
         <v>-4.1365046535677399</v>
       </c>
       <c r="AT7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AU7" s="32">
         <v>45922</v>
@@ -16429,7 +16433,7 @@
         <v>1.0432190760059601</v>
       </c>
       <c r="AY7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AZ7" s="32">
         <v>45929</v>
@@ -16444,7 +16448,7 @@
         <v>-10.649474689589301</v>
       </c>
       <c r="BD7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="BE7" s="32">
         <v>45936</v>
@@ -16459,7 +16463,7 @@
         <v>-11.4478114478114</v>
       </c>
       <c r="BI7" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="BJ7" s="32">
         <v>45943</v>
@@ -16506,7 +16510,7 @@
       <c r="CV7" s="18"/>
       <c r="CW7" s="17"/>
       <c r="DA7" s="91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="DB7" s="71">
         <f t="shared" si="0"/>
@@ -16525,7 +16529,7 @@
     </row>
     <row r="8" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="32">
         <v>45862</v>
@@ -16540,7 +16544,7 @@
         <v>-30.761572921851599</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" s="28">
         <v>45869</v>
@@ -16555,7 +16559,7 @@
         <v>-16.619074814391698</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="28">
         <v>45874</v>
@@ -16570,7 +16574,7 @@
         <v>-14.188124014713599</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="28">
         <v>45880</v>
@@ -16585,7 +16589,7 @@
         <v>-26.099706744868001</v>
       </c>
       <c r="U8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V8" s="32">
         <v>45886</v>
@@ -16600,7 +16604,7 @@
         <v>-29.236043095004799</v>
       </c>
       <c r="Z8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8" s="32">
         <v>45894</v>
@@ -16615,7 +16619,7 @@
         <v>-14.7575919019712</v>
       </c>
       <c r="AE8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF8" s="32">
         <v>45901</v>
@@ -16630,7 +16634,7 @@
         <v>-30.546792849631899</v>
       </c>
       <c r="AJ8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK8" s="32">
         <v>45908</v>
@@ -16645,7 +16649,7 @@
         <v>-24.368825466520299</v>
       </c>
       <c r="AO8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP8" s="32">
         <v>45915</v>
@@ -16660,7 +16664,7 @@
         <v>-25.252525252525199</v>
       </c>
       <c r="AT8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU8" s="32">
         <v>45922</v>
@@ -16675,7 +16679,7 @@
         <v>-16.7017913593256</v>
       </c>
       <c r="AY8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ8" s="32">
         <v>45929</v>
@@ -16690,7 +16694,7 @@
         <v>-25.5200405885337</v>
       </c>
       <c r="BD8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE8" s="32">
         <v>45936</v>
@@ -16705,7 +16709,7 @@
         <v>-12.8249566724436</v>
       </c>
       <c r="BI8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BJ8" s="32">
         <v>45943</v>
@@ -16720,7 +16724,7 @@
         <v>-10.5672969966629</v>
       </c>
       <c r="BN8" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BO8" s="32">
         <v>45950</v>
@@ -16735,7 +16739,7 @@
         <v>-10.106085985482901</v>
       </c>
       <c r="BS8" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT8" s="28">
         <v>45957</v>
@@ -16750,7 +16754,7 @@
         <v>-16.571428571428498</v>
       </c>
       <c r="BX8" s="129" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY8" s="117">
         <v>45964</v>
@@ -16765,7 +16769,7 @@
         <v>-5.7495969908651201</v>
       </c>
       <c r="CC8" s="141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CD8" s="135">
         <v>45971</v>
@@ -16780,7 +16784,7 @@
         <v>-6.5113816834303799</v>
       </c>
       <c r="CH8" s="141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CI8" s="135">
         <v>45978</v>
@@ -16800,7 +16804,7 @@
       <c r="CU8" s="19"/>
       <c r="CV8" s="18"/>
       <c r="DA8" s="69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DB8" s="71">
         <f t="shared" si="0"/>
@@ -16837,7 +16841,7 @@
     </row>
     <row r="9" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="32">
         <v>45862</v>
@@ -16852,7 +16856,7 @@
         <v>-28.5888572590483</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="28">
         <v>45869</v>
@@ -16867,7 +16871,7 @@
         <v>-31.202858277093998</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" s="28">
         <v>45874</v>
@@ -16882,7 +16886,7 @@
         <v>-30.844508880028901</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="28">
         <v>45880</v>
@@ -16897,7 +16901,7 @@
         <v>-30.379746835443001</v>
       </c>
       <c r="U9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V9" s="32">
         <v>45886</v>
@@ -16912,7 +16916,7 @@
         <v>-28.508449669360701</v>
       </c>
       <c r="Z9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="32">
         <v>45894</v>
@@ -16927,7 +16931,7 @@
         <v>-21.900826446280899</v>
       </c>
       <c r="AE9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF9" s="32">
         <v>45901</v>
@@ -16942,7 +16946,7 @@
         <v>-24.711639286962601</v>
       </c>
       <c r="AJ9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="32">
         <v>45908</v>
@@ -16957,7 +16961,7 @@
         <v>-27.5599128540305</v>
       </c>
       <c r="AO9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP9" s="32">
         <v>45915</v>
@@ -16972,7 +16976,7 @@
         <v>-22.126038781163398</v>
       </c>
       <c r="AT9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU9" s="32">
         <v>45922</v>
@@ -16987,7 +16991,7 @@
         <v>-13.632986627043</v>
       </c>
       <c r="AY9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ9" s="32">
         <v>45929</v>
@@ -17002,7 +17006,7 @@
         <v>-27.744982290436798</v>
       </c>
       <c r="BD9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE9" s="32">
         <v>45936</v>
@@ -17017,7 +17021,7 @@
         <v>-17.503692762186098</v>
       </c>
       <c r="BI9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BJ9" s="32">
         <v>45943</v>
@@ -17032,7 +17036,7 @@
         <v>-28.724162508909401</v>
       </c>
       <c r="BN9" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BO9" s="32">
         <v>45950</v>
@@ -17047,7 +17051,7 @@
         <v>-21.613727637823999</v>
       </c>
       <c r="BS9" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT9" s="28">
         <v>45957</v>
@@ -17062,7 +17066,7 @@
         <v>-19.7161488300728</v>
       </c>
       <c r="BX9" s="129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY9" s="117">
         <v>45964</v>
@@ -17077,7 +17081,7 @@
         <v>-19.690576652602001</v>
       </c>
       <c r="CC9" s="141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CD9" s="135">
         <v>45971</v>
@@ -17092,7 +17096,7 @@
         <v>-25.652472527472501</v>
       </c>
       <c r="CH9" s="141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CI9" s="135">
         <v>45978</v>
@@ -17114,7 +17118,7 @@
       <c r="CV9" s="18"/>
       <c r="CW9" s="17"/>
       <c r="DA9" s="69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DB9" s="71">
         <f t="shared" si="0"/>
@@ -17152,7 +17156,7 @@
     </row>
     <row r="10" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="32">
         <v>45862</v>
@@ -17167,7 +17171,7 @@
         <v>-11.4063777596075</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="28">
         <v>45869</v>
@@ -17182,7 +17186,7 @@
         <v>-4.5079980610761003</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L10" s="28">
         <v>45874</v>
@@ -17197,7 +17201,7 @@
         <v>-4.3232115285640704</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="28">
         <v>45880</v>
@@ -17212,7 +17216,7 @@
         <v>-12.2755741127348</v>
       </c>
       <c r="U10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V10" s="32">
         <v>45886</v>
@@ -17227,7 +17231,7 @@
         <v>-2.20245658619229</v>
       </c>
       <c r="Z10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA10" s="32">
         <v>45894</v>
@@ -17257,7 +17261,7 @@
       <c r="AR10" s="26"/>
       <c r="AS10" s="40"/>
       <c r="AT10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU10" s="32">
         <v>45922</v>
@@ -17272,7 +17276,7 @@
         <v>-11.069418386491501</v>
       </c>
       <c r="AY10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ10" s="32">
         <v>45929</v>
@@ -17287,7 +17291,7 @@
         <v>9.4265855777584697</v>
       </c>
       <c r="BD10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE10" s="32">
         <v>45936</v>
@@ -17302,7 +17306,7 @@
         <v>-9.8687408847836604</v>
       </c>
       <c r="BI10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BJ10" s="32">
         <v>45943</v>
@@ -17317,7 +17321,7 @@
         <v>-3.8905515177426202</v>
       </c>
       <c r="BN10" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BO10" s="32">
         <v>45950</v>
@@ -17332,7 +17336,7 @@
         <v>-9.6511627906976702</v>
       </c>
       <c r="BS10" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT10" s="28">
         <v>45957</v>
@@ -17347,7 +17351,7 @@
         <v>-0.22634676324128</v>
       </c>
       <c r="BX10" s="129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY10" s="117">
         <v>45964</v>
@@ -17362,7 +17366,7 @@
         <v>-13.175810973167801</v>
       </c>
       <c r="CC10" s="141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CD10" s="135">
         <v>45971</v>
@@ -17377,7 +17381,7 @@
         <v>-5.9991368148467803</v>
       </c>
       <c r="CH10" s="141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CI10" s="135">
         <v>45978</v>
@@ -17398,7 +17402,7 @@
       <c r="CU10" s="19"/>
       <c r="CV10" s="18"/>
       <c r="DA10" s="69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DB10" s="71">
         <f t="shared" si="0"/>
@@ -17435,7 +17439,7 @@
     </row>
     <row r="11" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="32">
         <v>45862</v>
@@ -17450,7 +17454,7 @@
         <v>-5.0950570342205204</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="28">
         <v>45869</v>
@@ -17465,7 +17469,7 @@
         <v>-2.9251700680272101</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L11" s="28">
         <v>45874</v>
@@ -17480,7 +17484,7 @@
         <v>-8.8253195374315307</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q11" s="28">
         <v>45880</v>
@@ -17495,7 +17499,7 @@
         <v>-16.675993284834899</v>
       </c>
       <c r="U11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V11" s="32">
         <v>45886</v>
@@ -17510,7 +17514,7 @@
         <v>-18.791574279379098</v>
       </c>
       <c r="Z11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA11" s="32">
         <v>45894</v>
@@ -17525,7 +17529,7 @@
         <v>0.50473186119873703</v>
       </c>
       <c r="AE11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF11" s="32">
         <v>45901</v>
@@ -17540,7 +17544,7 @@
         <v>-6.8399452804379604E-2</v>
       </c>
       <c r="AJ11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK11" s="32">
         <v>45908</v>
@@ -17555,7 +17559,7 @@
         <v>-27.5543478260869</v>
       </c>
       <c r="AO11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP11" s="32">
         <v>45915</v>
@@ -17570,7 +17574,7 @@
         <v>-10.239651416121999</v>
       </c>
       <c r="AT11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU11" s="32">
         <v>45922</v>
@@ -17585,7 +17589,7 @@
         <v>-19.1397849462365</v>
       </c>
       <c r="AY11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ11" s="32">
         <v>45929</v>
@@ -17600,7 +17604,7 @@
         <v>-8.7951807228915708</v>
       </c>
       <c r="BD11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE11" s="32">
         <v>45936</v>
@@ -17615,7 +17619,7 @@
         <v>-12.6690391459074</v>
       </c>
       <c r="BI11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BJ11" s="32">
         <v>45943</v>
@@ -17630,7 +17634,7 @@
         <v>-25.9462759462759</v>
       </c>
       <c r="BN11" s="35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BO11" s="32">
         <v>45950</v>
@@ -17645,7 +17649,7 @@
         <v>-1.65542611894543</v>
       </c>
       <c r="BS11" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BT11" s="28">
         <v>45957</v>
@@ -17660,7 +17664,7 @@
         <v>6.5659881812207804E-2</v>
       </c>
       <c r="BX11" s="129" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY11" s="117">
         <v>45964</v>
@@ -17675,7 +17679,7 @@
         <v>11.4942528735632</v>
       </c>
       <c r="CC11" s="141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CD11" s="135">
         <v>45971</v>
@@ -17690,7 +17694,7 @@
         <v>7.5585789871501802E-2</v>
       </c>
       <c r="CH11" s="141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CI11" s="135">
         <v>45978</v>
@@ -17711,7 +17715,7 @@
       <c r="CU11" s="19"/>
       <c r="CV11" s="18"/>
       <c r="DA11" s="69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="DB11" s="71">
         <f t="shared" si="0"/>
@@ -17748,7 +17752,7 @@
     </row>
     <row r="12" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="32">
         <v>45862</v>
@@ -17763,7 +17767,7 @@
         <v>-9.0909090909090899</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="28">
         <v>45869</v>
@@ -17778,7 +17782,7 @@
         <v>-22.1212121212121</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L12" s="28">
         <v>45874</v>
@@ -17793,7 +17797,7 @@
         <v>-21.1023622047244</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q12" s="28">
         <v>45880</v>
@@ -17808,7 +17812,7 @@
         <v>-15.0471960022209</v>
       </c>
       <c r="U12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V12" s="32">
         <v>45886</v>
@@ -17823,7 +17827,7 @@
         <v>-19.874715261958901</v>
       </c>
       <c r="Z12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA12" s="32">
         <v>45894</v>
@@ -17838,7 +17842,7 @@
         <v>4.56165359942979</v>
       </c>
       <c r="AE12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF12" s="32">
         <v>45901</v>
@@ -17853,7 +17857,7 @@
         <v>6.8504594820384197</v>
       </c>
       <c r="AJ12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK12" s="32">
         <v>45908</v>
@@ -17868,7 +17872,7 @@
         <v>-18.700667880995699</v>
       </c>
       <c r="AO12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP12" s="32">
         <v>45915</v>
@@ -17883,7 +17887,7 @@
         <v>-13.8339920948616</v>
       </c>
       <c r="AT12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU12" s="32">
         <v>45922</v>
@@ -17898,7 +17902,7 @@
         <v>-10.5623100303951</v>
       </c>
       <c r="AY12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ12" s="32">
         <v>45929</v>
@@ -17913,7 +17917,7 @@
         <v>-18.531228551818799</v>
       </c>
       <c r="BD12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE12" s="32">
         <v>45936</v>
@@ -17928,7 +17932,7 @@
         <v>-18.1044957472661</v>
       </c>
       <c r="BI12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BJ12" s="32">
         <v>45943</v>
@@ -17943,7 +17947,7 @@
         <v>-18.660880347179098</v>
       </c>
       <c r="BN12" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BO12" s="32">
         <v>45950</v>
@@ -17958,7 +17962,7 @@
         <v>-24.697644812221501</v>
       </c>
       <c r="BS12" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BT12" s="28">
         <v>45957</v>
@@ -17973,7 +17977,7 @@
         <v>-19.3363844393592</v>
       </c>
       <c r="BX12" s="129" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY12" s="117">
         <v>45964</v>
@@ -17988,7 +17992,7 @@
         <v>-12.849162011173201</v>
       </c>
       <c r="CC12" s="141" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CD12" s="135">
         <v>45971</v>
@@ -18003,7 +18007,7 @@
         <v>-7.81922525107605</v>
       </c>
       <c r="CH12" s="141" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CI12" s="135">
         <v>45978</v>
@@ -18024,7 +18028,7 @@
       <c r="CU12" s="19"/>
       <c r="CV12" s="18"/>
       <c r="DA12" s="69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="DB12" s="71">
         <f t="shared" si="0"/>
@@ -18061,7 +18065,7 @@
     </row>
     <row r="13" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="17">
         <v>45862</v>
@@ -18076,7 +18080,7 @@
         <v>5.7</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="28">
         <v>45869</v>
@@ -18091,7 +18095,7 @@
         <v>-6</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" s="28">
         <v>45874</v>
@@ -18136,7 +18140,7 @@
       <c r="AR13" s="26"/>
       <c r="AS13" s="40"/>
       <c r="AT13" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU13" s="32">
         <v>45922</v>
@@ -18151,7 +18155,7 @@
         <v>2.6380873866446799</v>
       </c>
       <c r="AY13" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ13" s="32">
         <v>45929</v>
@@ -18166,7 +18170,7 @@
         <v>-9.2178770949720708</v>
       </c>
       <c r="BD13" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE13" s="32">
         <v>45936</v>
@@ -18181,7 +18185,7 @@
         <v>1.5873015873015901</v>
       </c>
       <c r="BI13" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BJ13" s="32">
         <v>45943</v>
@@ -18196,7 +18200,7 @@
         <v>-5.08928571428571</v>
       </c>
       <c r="BN13" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BO13" s="32">
         <v>45950</v>
@@ -18211,7 +18215,7 @@
         <v>3.9396479463537299</v>
       </c>
       <c r="BS13" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BT13" s="28">
         <v>45957</v>
@@ -18226,7 +18230,7 @@
         <v>5.8631921824104198</v>
       </c>
       <c r="BX13" s="129" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY13" s="117">
         <v>45964</v>
@@ -18241,7 +18245,7 @@
         <v>-3.6050156739811898</v>
       </c>
       <c r="CC13" s="141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CD13" s="135">
         <v>45971</v>
@@ -18256,7 +18260,7 @@
         <v>-8.1858407079645996</v>
       </c>
       <c r="CH13" s="141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CI13" s="135">
         <v>45978</v>
@@ -18277,7 +18281,7 @@
       <c r="CU13" s="19"/>
       <c r="CV13" s="18"/>
       <c r="DA13" s="69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="DB13" s="71">
         <f t="shared" si="0"/>
@@ -18314,7 +18318,7 @@
     </row>
     <row r="14" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="32">
         <v>45862</v>
@@ -18329,7 +18333,7 @@
         <v>-16.475354490209298</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="28">
         <v>45869</v>
@@ -18344,7 +18348,7 @@
         <v>-14.079895219384399</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L14" s="28">
         <v>45874</v>
@@ -18359,7 +18363,7 @@
         <v>-17.025316455696199</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="28">
         <v>45880</v>
@@ -18374,7 +18378,7 @@
         <v>-12.8763613068545</v>
       </c>
       <c r="U14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V14" s="32">
         <v>45886</v>
@@ -18389,7 +18393,7 @@
         <v>-18.686296715741701</v>
       </c>
       <c r="Z14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA14" s="32">
         <v>45894</v>
@@ -18404,7 +18408,7 @@
         <v>-3.94500896592946</v>
       </c>
       <c r="AE14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AF14" s="32">
         <v>45901</v>
@@ -18419,7 +18423,7 @@
         <v>-5.5025678650036696</v>
       </c>
       <c r="AJ14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK14" s="32">
         <v>45908</v>
@@ -18434,7 +18438,7 @@
         <v>-21.4882943143812</v>
       </c>
       <c r="AO14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP14" s="32">
         <v>45915</v>
@@ -18449,7 +18453,7 @@
         <v>-18.399532710280301</v>
       </c>
       <c r="AT14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AU14" s="32">
         <v>45922</v>
@@ -18464,7 +18468,7 @@
         <v>-14.7869674185463</v>
       </c>
       <c r="AY14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AZ14" s="32">
         <v>45929</v>
@@ -18479,7 +18483,7 @@
         <v>-20.718069452619101</v>
       </c>
       <c r="BD14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BE14" s="32">
         <v>45936</v>
@@ -18494,7 +18498,7 @@
         <v>-21.046578493386999</v>
       </c>
       <c r="BI14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BJ14" s="32">
         <v>45943</v>
@@ -18509,7 +18513,7 @@
         <v>-26.067665002773101</v>
       </c>
       <c r="BN14" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BO14" s="32">
         <v>45950</v>
@@ -18524,7 +18528,7 @@
         <v>-23.9375</v>
       </c>
       <c r="BS14" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BT14" s="28">
         <v>45957</v>
@@ -18539,7 +18543,7 @@
         <v>-23.008849557522101</v>
       </c>
       <c r="BX14" s="129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BY14" s="117">
         <v>45964</v>
@@ -18554,7 +18558,7 @@
         <v>-25.809935205183599</v>
       </c>
       <c r="CC14" s="141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CD14" s="135">
         <v>45971</v>
@@ -18569,7 +18573,7 @@
         <v>-18.5206422018349</v>
       </c>
       <c r="CH14" s="141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CI14" s="135">
         <v>45978</v>
@@ -18591,7 +18595,7 @@
       <c r="CV14" s="18"/>
       <c r="CW14" s="17"/>
       <c r="DA14" s="69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="DB14" s="71">
         <f t="shared" si="0"/>
@@ -18628,7 +18632,7 @@
     </row>
     <row r="15" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="32">
         <v>45862</v>
@@ -18643,7 +18647,7 @@
         <v>-9.9025141097998901</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" s="28">
         <v>45869</v>
@@ -18658,7 +18662,7 @@
         <v>-5.0198807157057601</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L15" s="28">
         <v>45874</v>
@@ -18673,7 +18677,7 @@
         <v>-9.7423887587821998</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q15" s="28">
         <v>45880</v>
@@ -18688,7 +18692,7 @@
         <v>-8.5944919278252598</v>
       </c>
       <c r="U15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V15" s="32">
         <v>45886</v>
@@ -18703,7 +18707,7 @@
         <v>-13.9756944444444</v>
       </c>
       <c r="Z15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA15" s="32">
         <v>45894</v>
@@ -18718,7 +18722,7 @@
         <v>-10.437556973564201</v>
       </c>
       <c r="AE15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF15" s="32">
         <v>45901</v>
@@ -18733,7 +18737,7 @@
         <v>-8.0234833659491205</v>
       </c>
       <c r="AJ15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AK15" s="32">
         <v>45908</v>
@@ -18748,7 +18752,7 @@
         <v>-8.0589680589680608</v>
       </c>
       <c r="AO15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AP15" s="32">
         <v>45915</v>
@@ -18763,7 +18767,7 @@
         <v>-12.0949338201734</v>
       </c>
       <c r="AT15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AU15" s="32">
         <v>45922</v>
@@ -18778,7 +18782,7 @@
         <v>-9.2240911557243592</v>
       </c>
       <c r="AY15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ15" s="32">
         <v>45929</v>
@@ -18793,7 +18797,7 @@
         <v>-6.1882475299011901</v>
       </c>
       <c r="BD15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BE15" s="32">
         <v>45936</v>
@@ -18808,7 +18812,7 @@
         <v>-2.6595744680851001</v>
       </c>
       <c r="BI15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BJ15" s="32">
         <v>45943</v>
@@ -18823,7 +18827,7 @@
         <v>-1.3864818024263399</v>
       </c>
       <c r="BN15" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BO15" s="32">
         <v>45950</v>
@@ -18838,7 +18842,7 @@
         <v>-8.5972850678732993</v>
       </c>
       <c r="BS15" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BT15" s="28">
         <v>45957</v>
@@ -18853,7 +18857,7 @@
         <v>-0.52966101694915602</v>
       </c>
       <c r="BX15" s="129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BY15" s="117">
         <v>45964</v>
@@ -18868,7 +18872,7 @@
         <v>0.55248618784530301</v>
       </c>
       <c r="CC15" s="141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CD15" s="135">
         <v>45971</v>
@@ -18883,7 +18887,7 @@
         <v>0</v>
       </c>
       <c r="CH15" s="141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CI15" s="135">
         <v>45978</v>
@@ -18905,7 +18909,7 @@
       <c r="CV15" s="18"/>
       <c r="CW15" s="17"/>
       <c r="DA15" s="69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DB15" s="71">
         <f t="shared" si="0"/>
@@ -18942,7 +18946,7 @@
     </row>
     <row r="16" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A16" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B16" s="86">
         <v>45869</v>
@@ -18957,7 +18961,7 @@
         <v>-30.027548209366302</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="28">
         <v>45869</v>
@@ -18972,7 +18976,7 @@
         <v>-30.027548209366302</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L16" s="28">
         <v>45874</v>
@@ -18987,7 +18991,7 @@
         <v>-41.132075471698101</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q16" s="28">
         <v>45880</v>
@@ -19002,7 +19006,7 @@
         <v>-34.4115004492363</v>
       </c>
       <c r="U16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V16" s="32">
         <v>45886</v>
@@ -19017,7 +19021,7 @@
         <v>-38.229927007299203</v>
       </c>
       <c r="Z16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AA16" s="32">
         <v>45894</v>
@@ -19032,7 +19036,7 @@
         <v>-29.3087121212121</v>
       </c>
       <c r="AE16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AF16" s="32">
         <v>45901</v>
@@ -19062,7 +19066,7 @@
       <c r="AW16" s="27"/>
       <c r="AX16" s="40"/>
       <c r="AY16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AZ16" s="32">
         <v>45929</v>
@@ -19077,7 +19081,7 @@
         <v>-43.8538205980066</v>
       </c>
       <c r="BD16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BE16" s="32">
         <v>45936</v>
@@ -19097,7 +19101,7 @@
       <c r="BL16" s="27"/>
       <c r="BM16" s="40"/>
       <c r="BN16" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BO16" s="32">
         <v>45950</v>
@@ -19112,7 +19116,7 @@
         <v>-36.606708799222098</v>
       </c>
       <c r="BS16" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BT16" s="28">
         <v>45957</v>
@@ -19149,7 +19153,7 @@
       <c r="CV16" s="18"/>
       <c r="CW16" s="17"/>
       <c r="DA16" s="69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="DB16" s="71">
         <f t="shared" si="0"/>
@@ -19168,7 +19172,7 @@
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="32">
         <v>45862</v>
@@ -19183,7 +19187,7 @@
         <v>-14.6406984553391</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="28">
         <v>45869</v>
@@ -19198,7 +19202,7 @@
         <v>-9.5182138660399396</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L17" s="28">
         <v>45874</v>
@@ -19213,7 +19217,7 @@
         <v>-0.39087947882736601</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="28">
         <v>45880</v>
@@ -19228,7 +19232,7 @@
         <v>-20.475418692598499</v>
       </c>
       <c r="U17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V17" s="32">
         <v>45886</v>
@@ -19243,7 +19247,7 @@
         <v>-22.0713073005093</v>
       </c>
       <c r="Z17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA17" s="32">
         <v>45894</v>
@@ -19258,7 +19262,7 @@
         <v>-10.080896079651501</v>
       </c>
       <c r="AE17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF17" s="32">
         <v>45901</v>
@@ -19273,7 +19277,7 @@
         <v>-14.2086330935251</v>
       </c>
       <c r="AJ17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AK17" s="32">
         <v>45908</v>
@@ -19288,7 +19292,7 @@
         <v>-5.3333333333333304</v>
       </c>
       <c r="AO17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AP17" s="32">
         <v>45915</v>
@@ -19303,7 +19307,7 @@
         <v>-0.42857142857143299</v>
       </c>
       <c r="AT17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AU17" s="32">
         <v>45922</v>
@@ -19318,7 +19322,7 @@
         <v>-6.5128900949796504</v>
       </c>
       <c r="AY17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AZ17" s="32">
         <v>45929</v>
@@ -19333,7 +19337,7 @@
         <v>-4.6540110226576896</v>
       </c>
       <c r="BD17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BE17" s="32">
         <v>45936</v>
@@ -19348,7 +19352,7 @@
         <v>2.8027498677948102</v>
       </c>
       <c r="BI17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BJ17" s="32">
         <v>45943</v>
@@ -19363,7 +19367,7 @@
         <v>-10.265087422447801</v>
       </c>
       <c r="BN17" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BO17" s="32">
         <v>45950</v>
@@ -19378,7 +19382,7 @@
         <v>-8.6279209107249795</v>
       </c>
       <c r="BS17" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BT17" s="28">
         <v>45957</v>
@@ -19393,7 +19397,7 @@
         <v>1.42394822006473</v>
       </c>
       <c r="BX17" s="129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="BY17" s="117">
         <v>45964</v>
@@ -19408,7 +19412,7 @@
         <v>1.67865707434053</v>
       </c>
       <c r="CC17" s="141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CD17" s="135">
         <v>45971</v>
@@ -19434,7 +19438,7 @@
       <c r="CU17" s="19"/>
       <c r="CV17" s="18"/>
       <c r="DA17" s="69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="DB17" s="71">
         <f t="shared" si="0"/>
@@ -19453,7 +19457,7 @@
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B18" s="86">
         <v>45880</v>
@@ -19478,7 +19482,7 @@
       <c r="N18" s="27"/>
       <c r="O18" s="49"/>
       <c r="P18" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="28">
         <v>45880</v>
@@ -19493,7 +19497,7 @@
         <v>-3.3497536945812798</v>
       </c>
       <c r="U18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V18" s="32">
         <v>45886</v>
@@ -19513,7 +19517,7 @@
       <c r="AC18" s="26"/>
       <c r="AD18" s="40"/>
       <c r="AE18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AF18" s="32">
         <v>45901</v>
@@ -19528,7 +19532,7 @@
         <v>-3.3170731707317098</v>
       </c>
       <c r="AJ18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AK18" s="32">
         <v>45908</v>
@@ -19543,7 +19547,7 @@
         <v>17.088280846670099</v>
       </c>
       <c r="AO18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AP18" s="32">
         <v>45915</v>
@@ -19558,7 +19562,7 @@
         <v>7.7928607340371903</v>
       </c>
       <c r="AT18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AU18" s="32">
         <v>45922</v>
@@ -19573,7 +19577,7 @@
         <v>-1.82815356489944</v>
       </c>
       <c r="AY18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AZ18" s="32">
         <v>45929</v>
@@ -19588,7 +19592,7 @@
         <v>13.0072262367982</v>
       </c>
       <c r="BD18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BE18" s="32">
         <v>45936</v>
@@ -19603,7 +19607,7 @@
         <v>6.7673378076062596</v>
       </c>
       <c r="BI18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BJ18" s="32">
         <v>45943</v>
@@ -19618,7 +19622,7 @@
         <v>3.1887088342916798</v>
       </c>
       <c r="BN18" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BO18" s="32">
         <v>45950</v>
@@ -19660,7 +19664,7 @@
       <c r="CV18" s="18"/>
       <c r="CW18" s="17"/>
       <c r="DA18" s="69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="DB18" s="71">
         <f t="shared" si="0"/>
@@ -19679,7 +19683,7 @@
     </row>
     <row r="19" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="32">
         <v>45862</v>
@@ -19704,7 +19708,7 @@
       <c r="N19" s="27"/>
       <c r="O19" s="49"/>
       <c r="P19" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19" s="28">
         <v>45880</v>
@@ -19724,7 +19728,7 @@
       <c r="X19" s="26"/>
       <c r="Y19" s="40"/>
       <c r="Z19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA19" s="32">
         <v>45894</v>
@@ -19739,7 +19743,7 @@
         <v>-15.709342560553599</v>
       </c>
       <c r="AE19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AF19" s="32">
         <v>45901</v>
@@ -19754,7 +19758,7 @@
         <v>-20.5683355886332</v>
       </c>
       <c r="AJ19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AK19" s="32">
         <v>45908</v>
@@ -19769,7 +19773,7 @@
         <v>-31.8019093078758</v>
       </c>
       <c r="AO19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AP19" s="32">
         <v>45915</v>
@@ -19784,7 +19788,7 @@
         <v>-21.790123456790099</v>
       </c>
       <c r="AT19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AU19" s="32">
         <v>45922</v>
@@ -19846,7 +19850,7 @@
       <c r="CV19" s="18"/>
       <c r="CW19" s="17"/>
       <c r="DA19" s="69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="DB19" s="71">
         <f t="shared" si="0"/>
@@ -19865,7 +19869,7 @@
     </row>
     <row r="20" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="B20" s="32">
         <v>45862</v>
@@ -19880,7 +19884,7 @@
         <v>-23.037831733483898</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="G20" s="28">
         <v>45869</v>
@@ -19895,7 +19899,7 @@
         <v>-22.845055526176601</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="L20" s="28">
         <v>45874</v>
@@ -19910,7 +19914,7 @@
         <v>-14.881933003844001</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="28">
         <v>45880</v>
@@ -19925,7 +19929,7 @@
         <v>-24.476650563606999</v>
       </c>
       <c r="U20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="V20" s="32">
         <v>45886</v>
@@ -19940,7 +19944,7 @@
         <v>-21.013727560717999</v>
       </c>
       <c r="Z20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AA20" s="32">
         <v>45894</v>
@@ -19955,7 +19959,7 @@
         <v>-19.058295964125499</v>
       </c>
       <c r="AE20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AF20" s="32">
         <v>45901</v>
@@ -19970,7 +19974,7 @@
         <v>-18.508583690987098</v>
       </c>
       <c r="AJ20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AK20" s="32">
         <v>45908</v>
@@ -19995,7 +19999,7 @@
       <c r="AW20" s="27"/>
       <c r="AX20" s="40"/>
       <c r="AY20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="AZ20" s="32">
         <v>45929</v>
@@ -20010,7 +20014,7 @@
         <v>-4.3686006825938497</v>
       </c>
       <c r="BD20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BE20" s="32">
         <v>45937</v>
@@ -20030,7 +20034,7 @@
       <c r="BL20" s="27"/>
       <c r="BM20" s="40"/>
       <c r="BN20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BO20" s="32">
         <v>45950</v>
@@ -20045,7 +20049,7 @@
         <v>-8.6999999999999993</v>
       </c>
       <c r="BS20" s="35" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BT20" s="28">
         <v>45957</v>
@@ -20060,7 +20064,7 @@
         <v>-13.8</v>
       </c>
       <c r="BX20" s="129" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="BY20" s="117">
         <v>45964</v>
@@ -20075,7 +20079,7 @@
         <v>-7.7</v>
       </c>
       <c r="CC20" s="129" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="CD20" s="135">
         <v>45971</v>
@@ -20090,7 +20094,7 @@
         <v>-10</v>
       </c>
       <c r="CH20" s="129" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="CI20" s="135">
         <v>45978</v>
@@ -20112,7 +20116,7 @@
       <c r="CV20" s="18"/>
       <c r="CW20" s="17"/>
       <c r="DA20" s="69" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="DB20" s="71">
         <f t="shared" si="0"/>
@@ -20149,7 +20153,7 @@
     </row>
     <row r="21" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="32">
         <v>45862</v>
@@ -20164,7 +20168,7 @@
         <v>-12.9739336492891</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G21" s="28">
         <v>45869</v>
@@ -20179,7 +20183,7 @@
         <v>-17.6945244956772</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L21" s="28">
         <v>45874</v>
@@ -20194,7 +20198,7 @@
         <v>-16.398546964192999</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q21" s="28">
         <v>45880</v>
@@ -20209,7 +20213,7 @@
         <v>-13.9607032057911</v>
       </c>
       <c r="U21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V21" s="32">
         <v>45886</v>
@@ -20224,7 +20228,7 @@
         <v>-13.435281267067101</v>
       </c>
       <c r="Z21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA21" s="32">
         <v>45894</v>
@@ -20239,7 +20243,7 @@
         <v>-5.0488599348534198</v>
       </c>
       <c r="AE21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF21" s="32">
         <v>45901</v>
@@ -20254,7 +20258,7 @@
         <v>-6.2933025404157004</v>
       </c>
       <c r="AJ21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK21" s="32">
         <v>45908</v>
@@ -20269,7 +20273,7 @@
         <v>-14.935064935064901</v>
       </c>
       <c r="AO21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP21" s="32">
         <v>45915</v>
@@ -20284,7 +20288,7 @@
         <v>-17.4104683195592</v>
       </c>
       <c r="AT21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AU21" s="32">
         <v>45922</v>
@@ -20299,7 +20303,7 @@
         <v>-17.567567567567501</v>
       </c>
       <c r="AY21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AZ21" s="32">
         <v>45929</v>
@@ -20314,7 +20318,7 @@
         <v>-11.311983471074299</v>
       </c>
       <c r="BD21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE21" s="32">
         <v>45936</v>
@@ -20334,7 +20338,7 @@
       <c r="BL21" s="27"/>
       <c r="BM21" s="40"/>
       <c r="BN21" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BO21" s="32">
         <v>45950</v>
@@ -20349,7 +20353,7 @@
         <v>-20.505050505050502</v>
       </c>
       <c r="BS21" s="30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BT21" s="28">
         <v>45957</v>
@@ -20364,7 +20368,7 @@
         <v>-9.3385214007782107</v>
       </c>
       <c r="BX21" s="129" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY21" s="117">
         <v>45964</v>
@@ -20379,7 +20383,7 @@
         <v>-8.9230769230769198</v>
       </c>
       <c r="CC21" s="141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CD21" s="135">
         <v>45971</v>
@@ -20394,7 +20398,7 @@
         <v>-19.341563786008201</v>
       </c>
       <c r="CH21" s="141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CI21" s="135">
         <v>45978</v>
@@ -20416,7 +20420,7 @@
       <c r="CV21" s="18"/>
       <c r="CW21" s="17"/>
       <c r="DA21" s="69" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="DB21" s="71">
         <f t="shared" si="0"/>
@@ -20453,7 +20457,7 @@
     </row>
     <row r="22" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="32">
         <v>45862</v>
@@ -20468,7 +20472,7 @@
         <v>9.0561224489795809</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G22" s="28">
         <v>45869</v>
@@ -20483,7 +20487,7 @@
         <v>2.3243243243243201</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L22" s="28">
         <v>45874</v>
@@ -20498,7 +20502,7 @@
         <v>3.4914017717561099</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q22" s="28">
         <v>45880</v>
@@ -20510,10 +20514,10 @@
         <v>461.5</v>
       </c>
       <c r="T22" s="82" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U22" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V22" s="32">
         <v>45886</v>
@@ -20528,7 +20532,7 @@
         <v>-6.1213991769547302</v>
       </c>
       <c r="Z22" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA22" s="32">
         <v>45894</v>
@@ -20543,7 +20547,7 @@
         <v>-0.152983171851095</v>
       </c>
       <c r="AE22" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AF22" s="32">
         <v>45901</v>
@@ -20591,7 +20595,9 @@
       <c r="BO22" s="26"/>
       <c r="BP22" s="26"/>
       <c r="BQ22" s="26"/>
-      <c r="BR22" s="40"/>
+      <c r="BR22" s="40" t="s">
+        <v>79</v>
+      </c>
       <c r="BS22" s="30"/>
       <c r="BT22" s="27"/>
       <c r="BU22" s="27"/>
@@ -20619,7 +20625,7 @@
       <c r="CU22" s="19"/>
       <c r="CV22" s="18"/>
       <c r="DA22" s="69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="DB22" s="71">
         <f t="shared" si="0"/>
@@ -20693,7 +20699,7 @@
       <c r="BB23" s="27"/>
       <c r="BC23" s="40"/>
       <c r="BD23" s="35" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BE23" s="32">
         <v>45936</v>
@@ -20708,7 +20714,7 @@
         <v>-15.321983715766001</v>
       </c>
       <c r="BI23" s="35" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BJ23" s="32">
         <v>45943</v>
@@ -20723,7 +20729,7 @@
         <v>-18.124507486209598</v>
       </c>
       <c r="BN23" s="35" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BO23" s="32">
         <v>45950</v>
@@ -20738,7 +20744,7 @@
         <v>-18.362662586074901</v>
       </c>
       <c r="BS23" s="30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BT23" s="28">
         <v>45957</v>
@@ -20753,7 +20759,7 @@
         <v>-21.888412017167301</v>
       </c>
       <c r="BX23" s="129" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="BY23" s="117">
         <v>45964</v>
@@ -20768,7 +20774,7 @@
         <v>-30.109204368174701</v>
       </c>
       <c r="CC23" s="141" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="CD23" s="135">
         <v>45971</v>
@@ -20783,7 +20789,7 @@
         <v>-30.2611367127496</v>
       </c>
       <c r="CH23" s="141" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="CI23" s="135">
         <v>45978</v>
@@ -20804,7 +20810,7 @@
       <c r="CU23" s="19"/>
       <c r="CV23" s="18"/>
       <c r="DA23" s="69" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="DB23" s="71">
         <f t="shared" si="0"/>
@@ -20823,7 +20829,7 @@
     </row>
     <row r="24" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B24" s="32">
         <v>45862</v>
@@ -20838,7 +20844,7 @@
         <v>-7.1005917159763303</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="28">
         <v>45869</v>
@@ -20853,7 +20859,7 @@
         <v>-3.3629441624365399</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L24" s="28">
         <v>45874</v>
@@ -20868,7 +20874,7 @@
         <v>-17.3861620342992</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="28">
         <v>45880</v>
@@ -20883,7 +20889,7 @@
         <v>-14.665911664779101</v>
       </c>
       <c r="U24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="V24" s="32">
         <v>45886</v>
@@ -20898,7 +20904,7 @@
         <v>-11.6426512968299</v>
       </c>
       <c r="Z24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA24" s="32">
         <v>45894</v>
@@ -20913,7 +20919,7 @@
         <v>-0.289017341040465</v>
       </c>
       <c r="AE24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF24" s="32">
         <v>45901</v>
@@ -20928,7 +20934,7 @@
         <v>0.62578222778473203</v>
       </c>
       <c r="AJ24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK24" s="32">
         <v>45908</v>
@@ -20943,7 +20949,7 @@
         <v>-12.5838926174496</v>
       </c>
       <c r="AO24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP24" s="32">
         <v>45915</v>
@@ -20968,7 +20974,7 @@
       <c r="BB24" s="27"/>
       <c r="BC24" s="40"/>
       <c r="BD24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE24" s="32">
         <v>45936</v>
@@ -20983,7 +20989,7 @@
         <v>-10.5675146771037</v>
       </c>
       <c r="BI24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BJ24" s="32">
         <v>45943</v>
@@ -20998,7 +21004,7 @@
         <v>-13.699536730641899</v>
       </c>
       <c r="BN24" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BO24" s="32">
         <v>45950</v>
@@ -21013,7 +21019,7 @@
         <v>-19.372592184920201</v>
       </c>
       <c r="BS24" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BT24" s="28">
         <v>45957</v>
@@ -21028,7 +21034,7 @@
         <v>-15.768115942028899</v>
       </c>
       <c r="BX24" s="129" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY24" s="117">
         <v>45964</v>
@@ -21043,7 +21049,7 @@
         <v>-11.057692307692299</v>
       </c>
       <c r="CC24" s="141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CD24" s="135">
         <v>45971</v>
@@ -21058,7 +21064,7 @@
         <v>-12.914906457453201</v>
       </c>
       <c r="CH24" s="141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CI24" s="135">
         <v>45978</v>
@@ -21080,7 +21086,7 @@
       <c r="CV24" s="18"/>
       <c r="CW24" s="17"/>
       <c r="DA24" s="69" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="DB24" s="71">
         <f t="shared" si="0"/>
@@ -21117,7 +21123,7 @@
     </row>
     <row r="25" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="32">
         <v>45862</v>
@@ -21132,7 +21138,7 @@
         <v>-17.4766355140186</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="28">
         <v>45869</v>
@@ -21147,7 +21153,7 @@
         <v>-23.429819770617101</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L25" s="28">
         <v>45874</v>
@@ -21162,7 +21168,7 @@
         <v>-19.7796432318992</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q25" s="28">
         <v>45880</v>
@@ -21177,7 +21183,7 @@
         <v>-21.192758253461101</v>
       </c>
       <c r="U25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V25" s="32">
         <v>45886</v>
@@ -21192,7 +21198,7 @@
         <v>-16.855947399880399</v>
       </c>
       <c r="Z25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA25" s="32">
         <v>45894</v>
@@ -21207,7 +21213,7 @@
         <v>-23.329425556858101</v>
       </c>
       <c r="AE25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF25" s="32">
         <v>45901</v>
@@ -21222,7 +21228,7 @@
         <v>-20.511363636363601</v>
       </c>
       <c r="AJ25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK25" s="32">
         <v>45908</v>
@@ -21237,7 +21243,7 @@
         <v>-12.397734424166099</v>
       </c>
       <c r="AO25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AP25" s="32">
         <v>45915</v>
@@ -21252,7 +21258,7 @@
         <v>-30.732044198895</v>
       </c>
       <c r="AT25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU25" s="32">
         <v>45922</v>
@@ -21267,7 +21273,7 @@
         <v>-2.2364217252396101</v>
       </c>
       <c r="AY25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ25" s="32">
         <v>45929</v>
@@ -21282,7 +21288,7 @@
         <v>-7.0236039147956202</v>
       </c>
       <c r="BD25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE25" s="32">
         <v>45936</v>
@@ -21297,7 +21303,7 @@
         <v>-23.4574468085106</v>
       </c>
       <c r="BI25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BJ25" s="32">
         <v>45943</v>
@@ -21312,7 +21318,7 @@
         <v>-11.1443978430197</v>
       </c>
       <c r="BN25" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO25" s="32">
         <v>45950</v>
@@ -21327,7 +21333,7 @@
         <v>-5.1439069197795497</v>
       </c>
       <c r="BS25" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BT25" s="28">
         <v>45957</v>
@@ -21342,7 +21348,7 @@
         <v>-17.245901639344201</v>
       </c>
       <c r="BX25" s="129" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BY25" s="117">
         <v>45964</v>
@@ -21357,7 +21363,7 @@
         <v>-15.2063312605992</v>
       </c>
       <c r="CC25" s="141" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="CD25" s="135">
         <v>45971</v>
@@ -21372,7 +21378,7 @@
         <v>-15.375655212580099</v>
       </c>
       <c r="CH25" s="141" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="CI25" s="135">
         <v>45978</v>
@@ -21394,7 +21400,7 @@
       <c r="CV25" s="18"/>
       <c r="CW25" s="17"/>
       <c r="DA25" s="69" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="DB25" s="71">
         <f t="shared" si="0"/>
@@ -21431,7 +21437,7 @@
     </row>
     <row r="26" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B26" s="17">
         <v>45876</v>
@@ -21471,7 +21477,7 @@
       <c r="AC26" s="26"/>
       <c r="AD26" s="41"/>
       <c r="AE26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AF26" s="17">
         <v>45894</v>
@@ -21486,7 +21492,7 @@
         <v>-3.6676217765042902</v>
       </c>
       <c r="AJ26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AK26" s="17">
         <v>45908</v>
@@ -21501,7 +21507,7 @@
         <v>-15.643863179074399</v>
       </c>
       <c r="AO26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AP26" s="17">
         <v>45915</v>
@@ -21521,7 +21527,7 @@
       <c r="AW26" s="26"/>
       <c r="AX26" s="40"/>
       <c r="AY26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AZ26" s="17">
         <v>45929</v>
@@ -21536,7 +21542,7 @@
         <v>-10.5889014722536</v>
       </c>
       <c r="BD26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BE26" s="17">
         <v>45936</v>
@@ -21551,7 +21557,7 @@
         <v>-12.4569460390355</v>
       </c>
       <c r="BI26" s="35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BJ26" s="32">
         <v>45943</v>
@@ -21566,7 +21572,7 @@
         <v>-11.193181818181801</v>
       </c>
       <c r="BN26" s="35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BO26" s="32">
         <v>45950</v>
@@ -21581,7 +21587,7 @@
         <v>-11.9931467732724</v>
       </c>
       <c r="BS26" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BT26" s="28">
         <v>45957</v>
@@ -21596,7 +21602,7 @@
         <v>-17.0668058455114</v>
       </c>
       <c r="BX26" s="129" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="BY26" s="117">
         <v>45964</v>
@@ -21611,7 +21617,7 @@
         <v>-9.5483133218982292</v>
       </c>
       <c r="CC26" s="141" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="CD26" s="135">
         <v>45971</v>
@@ -21626,7 +21632,7 @@
         <v>-18.4623714131023</v>
       </c>
       <c r="CH26" s="141" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="CI26" s="135">
         <v>45978</v>
@@ -21648,7 +21654,7 @@
       <c r="CV26" s="18"/>
       <c r="CW26" s="17"/>
       <c r="DA26" s="69" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="DB26" s="71">
         <f t="shared" si="0"/>
@@ -21685,7 +21691,7 @@
     </row>
     <row r="27" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B27" s="86">
         <v>45880</v>
@@ -21710,7 +21716,7 @@
       <c r="N27" s="27"/>
       <c r="O27" s="49"/>
       <c r="P27" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q27" s="28">
         <v>45880</v>
@@ -21725,7 +21731,7 @@
         <v>-22.514868309260802</v>
       </c>
       <c r="U27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V27" s="32">
         <v>45886</v>
@@ -21740,7 +21746,7 @@
         <v>-34.595003785011301</v>
       </c>
       <c r="Z27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AA27" s="32">
         <v>45894</v>
@@ -21755,7 +21761,7 @@
         <v>-22.350993377483402</v>
       </c>
       <c r="AE27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AF27" s="32">
         <v>45901</v>
@@ -21770,7 +21776,7 @@
         <v>-24.7191011235955</v>
       </c>
       <c r="AJ27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AK27" s="32">
         <v>45908</v>
@@ -21785,7 +21791,7 @@
         <v>-27.0606531881804</v>
       </c>
       <c r="AO27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AP27" s="32">
         <v>45915</v>
@@ -21800,7 +21806,7 @@
         <v>-35.645041014168498</v>
       </c>
       <c r="AT27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AU27" s="32">
         <v>45922</v>
@@ -21815,7 +21821,7 @@
         <v>-17.236142748671199</v>
       </c>
       <c r="AY27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AZ27" s="32">
         <v>45929</v>
@@ -21830,7 +21836,7 @@
         <v>-6.8936170212765902</v>
       </c>
       <c r="BD27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BE27" s="32">
         <v>45936</v>
@@ -21845,7 +21851,7 @@
         <v>-12.2448979591836</v>
       </c>
       <c r="BI27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BJ27" s="32">
         <v>45943</v>
@@ -21860,7 +21866,7 @@
         <v>-19.0217391304347</v>
       </c>
       <c r="BN27" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BO27" s="32">
         <v>45950</v>
@@ -21875,7 +21881,7 @@
         <v>-20.573108008817002</v>
       </c>
       <c r="BS27" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BT27" s="28">
         <v>45957</v>
@@ -21890,7 +21896,7 @@
         <v>-14.831130690161499</v>
       </c>
       <c r="BX27" s="129" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BY27" s="117">
         <v>45964</v>
@@ -21905,7 +21911,7 @@
         <v>0.86893555394641497</v>
       </c>
       <c r="CC27" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="CD27" s="135">
         <v>45971</v>
@@ -21920,7 +21926,7 @@
         <v>-10.2280580511403</v>
       </c>
       <c r="CH27" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="CI27" s="135">
         <v>45978</v>
@@ -21942,7 +21948,7 @@
       <c r="CV27" s="18"/>
       <c r="CW27" s="17"/>
       <c r="DA27" s="69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="DB27" s="71">
         <f t="shared" si="0"/>
@@ -21979,7 +21985,7 @@
     </row>
     <row r="28" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" s="86">
         <v>45880</v>
@@ -22004,7 +22010,7 @@
       <c r="N28" s="27"/>
       <c r="O28" s="49"/>
       <c r="P28" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q28" s="28">
         <v>45880</v>
@@ -22019,7 +22025,7 @@
         <v>-9.6533333333333307</v>
       </c>
       <c r="U28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V28" s="32">
         <v>45886</v>
@@ -22034,7 +22040,7 @@
         <v>-3.3505154639175201</v>
       </c>
       <c r="Z28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA28" s="32">
         <v>45894</v>
@@ -22049,7 +22055,7 @@
         <v>11.764705882352899</v>
       </c>
       <c r="AE28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF28" s="32">
         <v>45901</v>
@@ -22064,7 +22070,7 @@
         <v>-10.893672537508101</v>
       </c>
       <c r="AJ28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK28" s="32">
         <v>45908</v>
@@ -22079,7 +22085,7 @@
         <v>-15.161725067385399</v>
       </c>
       <c r="AO28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AP28" s="32">
         <v>45915</v>
@@ -22094,7 +22100,7 @@
         <v>-4.3074884029158298</v>
       </c>
       <c r="AT28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AU28" s="32">
         <v>45922</v>
@@ -22109,7 +22115,7 @@
         <v>-3.7706205813040001</v>
       </c>
       <c r="AY28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AZ28" s="32">
         <v>45929</v>
@@ -22124,7 +22130,7 @@
         <v>-14.7720364741641</v>
       </c>
       <c r="BD28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BE28" s="32">
         <v>45936</v>
@@ -22144,7 +22150,7 @@
       <c r="BL28" s="27"/>
       <c r="BM28" s="40"/>
       <c r="BN28" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BO28" s="32">
         <v>45950</v>
@@ -22159,7 +22165,7 @@
         <v>-12.416717141126499</v>
       </c>
       <c r="BS28" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BT28" s="28">
         <v>45957</v>
@@ -22174,7 +22180,7 @@
         <v>-10.8669108669108</v>
       </c>
       <c r="BX28" s="129" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BY28" s="117">
         <v>45964</v>
@@ -22189,7 +22195,7 @@
         <v>-5.4250559284116404</v>
       </c>
       <c r="CC28" s="141" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="CD28" s="135">
         <v>45971</v>
@@ -22204,7 +22210,7 @@
         <v>-8.8284286507495899</v>
       </c>
       <c r="CH28" s="141" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="CI28" s="135">
         <v>45978</v>
@@ -22223,7 +22229,7 @@
       <c r="CU28" s="19"/>
       <c r="CV28" s="18"/>
       <c r="DA28" s="69" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="DB28" s="71">
         <f t="shared" si="0"/>
@@ -22260,7 +22266,7 @@
     </row>
     <row r="29" spans="1:113" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B29" s="32">
         <v>45862</v>
@@ -22275,7 +22281,7 @@
         <v>-2.3293172690763</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G29" s="28">
         <v>45869</v>
@@ -22290,7 +22296,7 @@
         <v>-15.344262295081901</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L29" s="28">
         <v>45874</v>
@@ -22305,7 +22311,7 @@
         <v>-11.76840780365</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q29" s="28">
         <v>45880</v>
@@ -22320,7 +22326,7 @@
         <v>-12.416717141126499</v>
       </c>
       <c r="U29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V29" s="32">
         <v>45886</v>
@@ -22335,7 +22341,7 @@
         <v>-17.776456599286501</v>
       </c>
       <c r="Z29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AA29" s="32">
         <v>45894</v>
@@ -22350,7 +22356,7 @@
         <v>-12.7750611246943</v>
       </c>
       <c r="AE29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF29" s="32">
         <v>45901</v>
@@ -22375,7 +22381,7 @@
       <c r="AR29" s="26"/>
       <c r="AS29" s="40"/>
       <c r="AT29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AU29" s="32">
         <v>45922</v>
@@ -22395,7 +22401,7 @@
       <c r="BB29" s="27"/>
       <c r="BC29" s="40"/>
       <c r="BD29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BE29" s="32">
         <v>45936</v>
@@ -22410,7 +22416,7 @@
         <v>-19.821958456973299</v>
       </c>
       <c r="BI29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ29" s="32">
         <v>45943</v>
@@ -22425,7 +22431,7 @@
         <v>-14.4827586206896</v>
       </c>
       <c r="BN29" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BO29" s="32">
         <v>45950</v>
@@ -22440,7 +22446,7 @@
         <v>-14.7992810065907</v>
       </c>
       <c r="BS29" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BT29" s="28">
         <v>45957</v>
@@ -22460,7 +22466,7 @@
       <c r="CA29" s="27"/>
       <c r="CB29" s="49"/>
       <c r="CC29" s="141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="CD29" s="135">
         <v>45971</v>
@@ -22475,7 +22481,7 @@
         <v>-27.067669172932298</v>
       </c>
       <c r="CH29" s="141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="CI29" s="135">
         <v>45978</v>
@@ -22504,7 +22510,7 @@
       <c r="CY29" s="23"/>
       <c r="CZ29" s="21"/>
       <c r="DA29" s="69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="DB29" s="71">
         <f t="shared" si="0"/>
@@ -22541,7 +22547,7 @@
     </row>
     <row r="30" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B30" s="32">
         <v>45862</v>
@@ -22556,7 +22562,7 @@
         <v>-12.285012285012201</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G30" s="28">
         <v>45869</v>
@@ -22571,7 +22577,7 @@
         <v>-14.9773071104387</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L30" s="28">
         <v>45874</v>
@@ -22586,7 +22592,7 @@
         <v>-14.6406984553391</v>
       </c>
       <c r="P30" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q30" s="28">
         <v>45880</v>
@@ -22601,7 +22607,7 @@
         <v>-20.106880427521698</v>
       </c>
       <c r="U30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V30" s="32">
         <v>45886</v>
@@ -22616,7 +22622,7 @@
         <v>-12.3774509803921</v>
       </c>
       <c r="Z30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA30" s="32">
         <v>45894</v>
@@ -22631,7 +22637,7 @@
         <v>-10.869565217391299</v>
       </c>
       <c r="AE30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF30" s="32">
         <v>45901</v>
@@ -22646,7 +22652,7 @@
         <v>-6.3110443275732502</v>
       </c>
       <c r="AJ30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK30" s="32">
         <v>45908</v>
@@ -22686,7 +22692,7 @@
       <c r="BL30" s="27"/>
       <c r="BM30" s="40"/>
       <c r="BN30" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BO30" s="32">
         <v>45950</v>
@@ -22701,7 +22707,7 @@
         <v>-25.601604278074799</v>
       </c>
       <c r="BS30" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BT30" s="28">
         <v>45957</v>
@@ -22716,7 +22722,7 @@
         <v>11.538461538461499</v>
       </c>
       <c r="BX30" s="129" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY30" s="117">
         <v>45964</v>
@@ -22731,7 +22737,7 @@
         <v>-10.7683352735739</v>
       </c>
       <c r="CC30" s="141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CD30" s="135">
         <v>45971</v>
@@ -22746,7 +22752,7 @@
         <v>-18.381010346926399</v>
       </c>
       <c r="CH30" s="141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CI30" s="135">
         <v>45978</v>
@@ -22761,7 +22767,7 @@
         <v>-10.338785046729001</v>
       </c>
       <c r="DA30" s="69" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="DB30" s="71">
         <f t="shared" si="0"/>
@@ -22798,7 +22804,7 @@
     </row>
     <row r="31" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B31" s="32">
         <v>45862</v>
@@ -22813,7 +22819,7 @@
         <v>5.5637982195845703</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G31" s="28">
         <v>45869</v>
@@ -22828,7 +22834,7 @@
         <v>-8.2352941176470598</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L31" s="28">
         <v>45874</v>
@@ -22843,7 +22849,7 @@
         <v>-10.9191430545957</v>
       </c>
       <c r="P31" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="28">
         <v>45880</v>
@@ -22858,7 +22864,7 @@
         <v>-5.7516339869281001</v>
       </c>
       <c r="U31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V31" s="32">
         <v>45886</v>
@@ -22873,7 +22879,7 @@
         <v>-23.4259784458309</v>
       </c>
       <c r="Z31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA31" s="32">
         <v>45894</v>
@@ -22888,7 +22894,7 @@
         <v>-11.884984025559101</v>
       </c>
       <c r="AE31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AF31" s="32">
         <v>45901</v>
@@ -22903,7 +22909,7 @@
         <v>-2.6188835286009602</v>
       </c>
       <c r="AJ31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK31" s="32">
         <v>45908</v>
@@ -22918,7 +22924,7 @@
         <v>-6.15491009681881</v>
       </c>
       <c r="AO31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AP31" s="32">
         <v>45915</v>
@@ -22933,7 +22939,7 @@
         <v>-8.8823094004441092</v>
       </c>
       <c r="AT31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AU31" s="32">
         <v>45922</v>
@@ -22948,7 +22954,7 @@
         <v>-0.83713850837138204</v>
       </c>
       <c r="AY31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AZ31" s="32">
         <v>45929</v>
@@ -22963,7 +22969,7 @@
         <v>0.368731563421831</v>
       </c>
       <c r="BD31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BE31" s="32">
         <v>45936</v>
@@ -22978,7 +22984,7 @@
         <v>-7.8091106290672396</v>
       </c>
       <c r="BI31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BJ31" s="32">
         <v>45943</v>
@@ -22993,7 +22999,7 @@
         <v>-10.951403148528399</v>
       </c>
       <c r="BN31" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BO31" s="32">
         <v>45950</v>
@@ -23008,7 +23014,7 @@
         <v>-0.17482517482517701</v>
       </c>
       <c r="BS31" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BT31" s="28">
         <v>45957</v>
@@ -23023,7 +23029,7 @@
         <v>-11.398544866612699</v>
       </c>
       <c r="BX31" s="129" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BY31" s="117">
         <v>45964</v>
@@ -23038,7 +23044,7 @@
         <v>20.3148425787106</v>
       </c>
       <c r="CC31" s="141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CD31" s="135">
         <v>45971</v>
@@ -23053,7 +23059,7 @@
         <v>-8.3577712609970707</v>
       </c>
       <c r="CH31" s="141" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CI31" s="135">
         <v>45978</v>
@@ -23068,7 +23074,7 @@
         <v>-17.638036809816001</v>
       </c>
       <c r="DA31" s="69" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="DB31" s="71">
         <f t="shared" si="0"/>
@@ -23105,7 +23111,7 @@
     </row>
     <row r="32" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A32" s="35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B32" s="107">
         <v>45886</v>
@@ -23135,7 +23141,7 @@
       <c r="S32" s="105"/>
       <c r="T32" s="106"/>
       <c r="U32" s="35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="V32" s="32">
         <v>45886</v>
@@ -23180,7 +23186,7 @@
       <c r="BB32" s="101"/>
       <c r="BC32" s="102"/>
       <c r="BD32" s="35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BE32" s="32">
         <v>45936</v>
@@ -23200,7 +23206,7 @@
       <c r="BL32" s="101"/>
       <c r="BM32" s="102"/>
       <c r="BN32" s="35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BO32" s="32">
         <v>45950</v>
@@ -23215,7 +23221,7 @@
         <v>-6.9252077562326804</v>
       </c>
       <c r="BS32" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BT32" s="28">
         <v>45957</v>
@@ -23230,7 +23236,7 @@
         <v>-5.2747252747252702</v>
       </c>
       <c r="BX32" s="129" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BY32" s="117">
         <v>45964</v>
@@ -23250,7 +23256,7 @@
       <c r="CF32" s="27"/>
       <c r="CG32" s="49"/>
       <c r="CH32" s="141" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="CI32" s="135">
         <v>45978</v>
@@ -23265,7 +23271,7 @@
         <v>-6.0810810810810896</v>
       </c>
       <c r="DA32" s="69" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="DB32" s="71">
         <f t="shared" si="0"/>
@@ -23302,7 +23308,7 @@
     </row>
     <row r="33" spans="1:113" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="37">
         <v>45862</v>
@@ -23317,7 +23323,7 @@
         <v>-4.5489591364687696</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G33" s="44">
         <v>45869</v>
@@ -23332,7 +23338,7 @@
         <v>1.2400354295836999</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L33" s="44">
         <v>45874</v>
@@ -23347,7 +23353,7 @@
         <v>-8.0134680134680103</v>
       </c>
       <c r="P33" s="43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q33" s="44">
         <v>45880</v>
@@ -23359,10 +23365,10 @@
         <v>362.25</v>
       </c>
       <c r="T33" s="83" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="V33" s="37">
         <v>45886</v>
@@ -23377,7 +23383,7 @@
         <v>-14.1002949852507</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA33" s="37">
         <v>45894</v>
@@ -23392,7 +23398,7 @@
         <v>3.4712950600801</v>
       </c>
       <c r="AE33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF33" s="37">
         <v>45901</v>
@@ -23407,7 +23413,7 @@
         <v>5.2374301675977604</v>
       </c>
       <c r="AJ33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK33" s="37">
         <v>45908</v>
@@ -23422,7 +23428,7 @@
         <v>0.28985507246376202</v>
       </c>
       <c r="AO33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP33" s="37">
         <v>45915</v>
@@ -23437,7 +23443,7 @@
         <v>-4.23880597014925</v>
       </c>
       <c r="AT33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AU33" s="37">
         <v>45922</v>
@@ -23452,7 +23458,7 @@
         <v>-11.3427345187001</v>
       </c>
       <c r="AY33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AZ33" s="37">
         <v>45929</v>
@@ -23467,7 +23473,7 @@
         <v>-5.4870530209617696</v>
       </c>
       <c r="BD33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE33" s="37">
         <v>45936</v>
@@ -23482,7 +23488,7 @@
         <v>8.3155650319829402</v>
       </c>
       <c r="BI33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BJ33" s="37">
         <v>45943</v>
@@ -23497,7 +23503,7 @@
         <v>-7.5903614457831301</v>
       </c>
       <c r="BN33" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BO33" s="37">
         <v>45950</v>
@@ -23512,7 +23518,7 @@
         <v>-0.56746532156368701</v>
       </c>
       <c r="BS33" s="43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BT33" s="44">
         <v>45957</v>
@@ -23527,7 +23533,7 @@
         <v>-6.2048192771084301</v>
       </c>
       <c r="BX33" s="130" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY33" s="124">
         <v>45964</v>
@@ -23547,7 +23553,7 @@
       <c r="CF33" s="45"/>
       <c r="CG33" s="50"/>
       <c r="CH33" s="143" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CI33" s="144">
         <v>45978</v>
@@ -23562,7 +23568,7 @@
         <v>-8.9452603471294996</v>
       </c>
       <c r="DA33" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="DB33" s="72">
         <f t="shared" si="0"/>
@@ -23605,7 +23611,7 @@
     </row>
     <row r="35" spans="1:113" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C35">
         <f>AVERAGE(C2:C33)</f>
@@ -23785,21 +23791,21 @@
       </c>
     </row>
     <row r="36" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="DD36" s="155">
+      <c r="DD36" s="159">
         <f>AVERAGE(DD35:DE35)</f>
         <v>-1.0871122196460784E-2</v>
       </c>
-      <c r="DE36" s="156"/>
-      <c r="DF36" s="155">
+      <c r="DE36" s="160"/>
+      <c r="DF36" s="159">
         <f>AVERAGE(DF35:DG35)</f>
         <v>-1.4613088654460921E-2</v>
       </c>
-      <c r="DG36" s="156"/>
-      <c r="DH36" s="155">
+      <c r="DG36" s="160"/>
+      <c r="DH36" s="159">
         <f>AVERAGE(DH35:DI35)</f>
         <v>2.73704760959292E-2</v>
       </c>
-      <c r="DI36" s="156"/>
+      <c r="DI36" s="160"/>
     </row>
     <row r="38" spans="1:113" x14ac:dyDescent="0.2">
       <c r="DI38" s="4"/>
